--- a/research/traditional_assets/database/data/finland/finland_chemical_diversified.xlsx
+++ b/research/traditional_assets/database/data/finland/finland_chemical_diversified.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08716011268335616</v>
+        <v>0.08702179245798945</v>
       </c>
       <c r="C2">
-        <v>3851.362924945516</v>
+        <v>3818.028522338605</v>
       </c>
       <c r="D2">
-        <v>3367.762924945516</v>
+        <v>3373.838522338605</v>
       </c>
       <c r="E2">
-        <v>-829.1</v>
+        <v>-789.6900000000001</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>39.41</v>
       </c>
       <c r="G2">
         <v>483.6</v>
@@ -1457,28 +1457,28 @@
         <v>298</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>1.982323</v>
       </c>
       <c r="N2">
-        <v>298</v>
+        <v>296.017677</v>
       </c>
       <c r="O2">
-        <v>59.6</v>
+        <v>59.2035354</v>
       </c>
       <c r="P2">
-        <v>238.4</v>
+        <v>236.8141416</v>
       </c>
       <c r="Q2">
-        <v>448</v>
+        <v>446.4141416</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08716011268335616</v>
+        <v>0.08749433581615096</v>
       </c>
       <c r="T2">
-        <v>0.8504074490426664</v>
+        <v>0.8572794284288698</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>150.3286800385204</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08702179245798945</v>
+        <v>0.08688347223262273</v>
       </c>
       <c r="C3">
-        <v>3818.028522338605</v>
+        <v>3784.716080657911</v>
       </c>
       <c r="D3">
-        <v>3373.838522338605</v>
+        <v>3379.936080657912</v>
       </c>
       <c r="E3">
-        <v>-789.6900000000001</v>
+        <v>-750.28</v>
       </c>
       <c r="F3">
-        <v>39.41</v>
+        <v>78.82000000000001</v>
       </c>
       <c r="G3">
         <v>483.6</v>
@@ -1539,28 +1539,28 @@
         <v>298</v>
       </c>
       <c r="M3">
-        <v>1.982323</v>
+        <v>3.964646</v>
       </c>
       <c r="N3">
-        <v>296.017677</v>
+        <v>294.035354</v>
       </c>
       <c r="O3">
-        <v>59.2035354</v>
+        <v>58.8070708</v>
       </c>
       <c r="P3">
-        <v>236.8141416</v>
+        <v>235.2282832</v>
       </c>
       <c r="Q3">
-        <v>446.4141416</v>
+        <v>444.8282832</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08749433581615096</v>
+        <v>0.08783537982920687</v>
       </c>
       <c r="T3">
-        <v>0.8572794284288698</v>
+        <v>0.8642916522923426</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>150.3286800385204</v>
+        <v>75.16434001926022</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08688347223262273</v>
+        <v>0.08674515200725604</v>
       </c>
       <c r="C4">
-        <v>3784.716080657911</v>
+        <v>3751.425719189356</v>
       </c>
       <c r="D4">
-        <v>3379.936080657912</v>
+        <v>3386.055719189356</v>
       </c>
       <c r="E4">
-        <v>-750.28</v>
+        <v>-710.87</v>
       </c>
       <c r="F4">
-        <v>78.82000000000001</v>
+        <v>118.23</v>
       </c>
       <c r="G4">
         <v>483.6</v>
@@ -1621,28 +1621,28 @@
         <v>298</v>
       </c>
       <c r="M4">
-        <v>3.964646</v>
+        <v>5.946968999999999</v>
       </c>
       <c r="N4">
-        <v>294.035354</v>
+        <v>292.053031</v>
       </c>
       <c r="O4">
-        <v>58.8070708</v>
+        <v>58.4106062</v>
       </c>
       <c r="P4">
-        <v>235.2282832</v>
+        <v>233.6424248</v>
       </c>
       <c r="Q4">
-        <v>444.8282832</v>
+        <v>443.2424248</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08783537982920687</v>
+        <v>0.08818345567758354</v>
       </c>
       <c r="T4">
-        <v>0.8642916522923426</v>
+        <v>0.8714484580911447</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>75.16434001926022</v>
+        <v>50.10956001284016</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08674515200725604</v>
+        <v>0.08660683178188931</v>
       </c>
       <c r="C5">
-        <v>3751.425719189356</v>
+        <v>3718.157558084336</v>
       </c>
       <c r="D5">
-        <v>3386.055719189356</v>
+        <v>3392.197558084335</v>
       </c>
       <c r="E5">
-        <v>-710.87</v>
+        <v>-671.46</v>
       </c>
       <c r="F5">
-        <v>118.23</v>
+        <v>157.64</v>
       </c>
       <c r="G5">
         <v>483.6</v>
@@ -1703,28 +1703,28 @@
         <v>298</v>
       </c>
       <c r="M5">
-        <v>5.946968999999999</v>
+        <v>7.929292</v>
       </c>
       <c r="N5">
-        <v>292.053031</v>
+        <v>290.070708</v>
       </c>
       <c r="O5">
-        <v>58.4106062</v>
+        <v>58.01414160000001</v>
       </c>
       <c r="P5">
-        <v>233.6424248</v>
+        <v>232.0565664</v>
       </c>
       <c r="Q5">
-        <v>443.2424248</v>
+        <v>441.6565664</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08818345567758354</v>
+        <v>0.08853878310613471</v>
       </c>
       <c r="T5">
-        <v>0.8714484580911447</v>
+        <v>0.8787543640107554</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>50.10956001284016</v>
+        <v>37.58217000963012</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08660683178188931</v>
+        <v>0.0864685115565226</v>
       </c>
       <c r="C6">
-        <v>3718.157558084336</v>
+        <v>3684.911718367578</v>
       </c>
       <c r="D6">
-        <v>3392.197558084335</v>
+        <v>3398.361718367579</v>
       </c>
       <c r="E6">
-        <v>-671.46</v>
+        <v>-632.05</v>
       </c>
       <c r="F6">
-        <v>157.64</v>
+        <v>197.05</v>
       </c>
       <c r="G6">
         <v>483.6</v>
@@ -1785,28 +1785,28 @@
         <v>298</v>
       </c>
       <c r="M6">
-        <v>7.929292</v>
+        <v>9.911614999999999</v>
       </c>
       <c r="N6">
-        <v>290.070708</v>
+        <v>288.088385</v>
       </c>
       <c r="O6">
-        <v>58.01414160000001</v>
+        <v>57.61767700000001</v>
       </c>
       <c r="P6">
-        <v>232.0565664</v>
+        <v>230.470708</v>
       </c>
       <c r="Q6">
-        <v>441.6565664</v>
+        <v>440.070708</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08853878310613471</v>
+        <v>0.08890159111212906</v>
       </c>
       <c r="T6">
-        <v>0.8787543640107554</v>
+        <v>0.8862140784760417</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>37.58217000963012</v>
+        <v>30.0657360077041</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.0864685115565226</v>
+        <v>0.08633019133115588</v>
       </c>
       <c r="C7">
-        <v>3684.911718367578</v>
+        <v>3651.688321945105</v>
       </c>
       <c r="D7">
-        <v>3398.361718367579</v>
+        <v>3404.548321945105</v>
       </c>
       <c r="E7">
-        <v>-632.05</v>
+        <v>-592.64</v>
       </c>
       <c r="F7">
-        <v>197.05</v>
+        <v>236.46</v>
       </c>
       <c r="G7">
         <v>483.6</v>
@@ -1867,28 +1867,28 @@
         <v>298</v>
       </c>
       <c r="M7">
-        <v>9.911614999999999</v>
+        <v>11.893938</v>
       </c>
       <c r="N7">
-        <v>288.088385</v>
+        <v>286.106062</v>
       </c>
       <c r="O7">
-        <v>57.61767700000001</v>
+        <v>57.22121240000001</v>
       </c>
       <c r="P7">
-        <v>230.470708</v>
+        <v>228.8848496</v>
       </c>
       <c r="Q7">
-        <v>440.070708</v>
+        <v>438.4848496</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08890159111212906</v>
+        <v>0.08927211843739988</v>
       </c>
       <c r="T7">
-        <v>0.8862140784760417</v>
+        <v>0.8938325102703771</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>30.0657360077041</v>
+        <v>25.05478000642008</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08633019133115588</v>
+        <v>0.08619187110578917</v>
       </c>
       <c r="C8">
-        <v>3651.688321945105</v>
+        <v>3618.487491612252</v>
       </c>
       <c r="D8">
-        <v>3404.548321945105</v>
+        <v>3410.757491612252</v>
       </c>
       <c r="E8">
-        <v>-592.6400000000001</v>
+        <v>-553.23</v>
       </c>
       <c r="F8">
-        <v>236.46</v>
+        <v>275.8699999999999</v>
       </c>
       <c r="G8">
         <v>483.6</v>
@@ -1949,28 +1949,28 @@
         <v>298</v>
       </c>
       <c r="M8">
-        <v>11.893938</v>
+        <v>13.876261</v>
       </c>
       <c r="N8">
-        <v>286.106062</v>
+        <v>284.123739</v>
       </c>
       <c r="O8">
-        <v>57.22121240000001</v>
+        <v>56.8247478</v>
       </c>
       <c r="P8">
-        <v>228.8848496</v>
+        <v>227.2989912</v>
       </c>
       <c r="Q8">
-        <v>438.4848496</v>
+        <v>436.8989912</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08927211843739988</v>
+        <v>0.08965061409224642</v>
       </c>
       <c r="T8">
-        <v>0.8938325102703771</v>
+        <v>0.9016147793076013</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>25.05478000642008</v>
+        <v>21.47552571978864</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08619187110578916</v>
+        <v>0.08605355088042248</v>
       </c>
       <c r="C9">
-        <v>3618.487491612252</v>
+        <v>3585.309351061805</v>
       </c>
       <c r="D9">
-        <v>3410.757491612252</v>
+        <v>3416.989351061805</v>
       </c>
       <c r="E9">
-        <v>-553.23</v>
+        <v>-513.8199999999999</v>
       </c>
       <c r="F9">
-        <v>275.87</v>
+        <v>315.28</v>
       </c>
       <c r="G9">
         <v>483.6</v>
@@ -2031,28 +2031,28 @@
         <v>298</v>
       </c>
       <c r="M9">
-        <v>13.876261</v>
+        <v>15.858584</v>
       </c>
       <c r="N9">
-        <v>284.123739</v>
+        <v>282.141416</v>
       </c>
       <c r="O9">
-        <v>56.8247478</v>
+        <v>56.4282832</v>
       </c>
       <c r="P9">
-        <v>227.2989912</v>
+        <v>225.7131328</v>
       </c>
       <c r="Q9">
-        <v>436.8989912</v>
+        <v>435.3131327999999</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08965061409224642</v>
+        <v>0.09003733791350269</v>
       </c>
       <c r="T9">
-        <v>0.9016147793076013</v>
+        <v>0.9095662281065041</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>21.47552571978864</v>
+        <v>18.79108500481506</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08605355088042248</v>
+        <v>0.08591523065505577</v>
       </c>
       <c r="C10">
-        <v>3585.309351061805</v>
+        <v>3552.154024892212</v>
       </c>
       <c r="D10">
-        <v>3416.989351061805</v>
+        <v>3423.244024892212</v>
       </c>
       <c r="E10">
-        <v>-513.8199999999999</v>
+        <v>-474.41</v>
       </c>
       <c r="F10">
-        <v>315.28</v>
+        <v>354.69</v>
       </c>
       <c r="G10">
         <v>483.6</v>
@@ -2113,28 +2113,28 @@
         <v>298</v>
       </c>
       <c r="M10">
-        <v>15.858584</v>
+        <v>17.840907</v>
       </c>
       <c r="N10">
-        <v>282.141416</v>
+        <v>280.159093</v>
       </c>
       <c r="O10">
-        <v>56.4282832</v>
+        <v>56.0318186</v>
       </c>
       <c r="P10">
-        <v>225.7131328</v>
+        <v>224.1272744</v>
       </c>
       <c r="Q10">
-        <v>435.3131327999999</v>
+        <v>433.7272743999999</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09003733791350269</v>
+        <v>0.09043256115940193</v>
       </c>
       <c r="T10">
-        <v>0.9095662281065041</v>
+        <v>0.9176924340218663</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>18.79108500481506</v>
+        <v>16.70318667094672</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08591523065505577</v>
+        <v>0.08577691042968905</v>
       </c>
       <c r="C11">
-        <v>3552.154024892212</v>
+        <v>3519.021638615885</v>
       </c>
       <c r="D11">
-        <v>3423.244024892212</v>
+        <v>3429.521638615885</v>
       </c>
       <c r="E11">
-        <v>-474.41</v>
+        <v>-435.0000000000001</v>
       </c>
       <c r="F11">
-        <v>354.69</v>
+        <v>394.1</v>
       </c>
       <c r="G11">
         <v>483.6</v>
@@ -2195,28 +2195,28 @@
         <v>298</v>
       </c>
       <c r="M11">
-        <v>17.840907</v>
+        <v>19.82323</v>
       </c>
       <c r="N11">
-        <v>280.159093</v>
+        <v>278.17677</v>
       </c>
       <c r="O11">
-        <v>56.0318186</v>
+        <v>55.635354</v>
       </c>
       <c r="P11">
-        <v>224.1272744</v>
+        <v>222.541416</v>
       </c>
       <c r="Q11">
-        <v>433.7272743999999</v>
+        <v>432.1414159999999</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09043256115940193</v>
+        <v>0.09083656714409893</v>
       </c>
       <c r="T11">
-        <v>0.9176924340218663</v>
+        <v>0.9259992222909034</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>16.70318667094672</v>
+        <v>15.03286800385205</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08577691042968905</v>
+        <v>0.08563859020432231</v>
       </c>
       <c r="C12">
-        <v>3519.021638615885</v>
+        <v>3485.912318667593</v>
       </c>
       <c r="D12">
-        <v>3429.521638615885</v>
+        <v>3435.822318667593</v>
       </c>
       <c r="E12">
-        <v>-435</v>
+        <v>-395.59</v>
       </c>
       <c r="F12">
-        <v>394.1</v>
+        <v>433.51</v>
       </c>
       <c r="G12">
         <v>483.6</v>
@@ -2277,28 +2277,28 @@
         <v>298</v>
       </c>
       <c r="M12">
-        <v>19.82323</v>
+        <v>21.805553</v>
       </c>
       <c r="N12">
-        <v>278.17677</v>
+        <v>276.194447</v>
       </c>
       <c r="O12">
-        <v>55.635354</v>
+        <v>55.23888940000001</v>
       </c>
       <c r="P12">
-        <v>222.541416</v>
+        <v>220.9555576</v>
       </c>
       <c r="Q12">
-        <v>432.1414159999999</v>
+        <v>430.5555576</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09083656714409893</v>
+        <v>0.09124965191496889</v>
       </c>
       <c r="T12">
-        <v>0.9259992222909035</v>
+        <v>0.9344926799592446</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>15.03286800385205</v>
+        <v>13.6662436398655</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08563859020432231</v>
+        <v>0.08564426997895562</v>
       </c>
       <c r="C13">
-        <v>3485.912318667593</v>
+        <v>3446.243141207244</v>
       </c>
       <c r="D13">
-        <v>3435.822318667593</v>
+        <v>3435.563141207244</v>
       </c>
       <c r="E13">
-        <v>-395.59</v>
+        <v>-356.1800000000001</v>
       </c>
       <c r="F13">
-        <v>433.51</v>
+        <v>472.92</v>
       </c>
       <c r="G13">
         <v>483.6</v>
@@ -2359,45 +2359,45 @@
         <v>298</v>
       </c>
       <c r="M13">
-        <v>21.805553</v>
+        <v>24.497256</v>
       </c>
       <c r="N13">
-        <v>276.194447</v>
+        <v>273.502744</v>
       </c>
       <c r="O13">
-        <v>55.23888940000001</v>
+        <v>54.70054880000001</v>
       </c>
       <c r="P13">
-        <v>220.9555576</v>
+        <v>218.8021952</v>
       </c>
       <c r="Q13">
-        <v>430.5555576</v>
+        <v>428.4021952</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09124965191496889</v>
+        <v>0.09167212497608593</v>
       </c>
       <c r="T13">
-        <v>0.9344926799592446</v>
+        <v>0.9431791707564119</v>
       </c>
       <c r="U13">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V13">
         <v>0.2</v>
       </c>
       <c r="W13">
-        <v>0.04024</v>
+        <v>0.04144</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y13">
-        <v>13.6662436398655</v>
+        <v>12.16462774442983</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08564426997895562</v>
+        <v>0.0855179497535889</v>
       </c>
       <c r="C14">
-        <v>3446.243141207244</v>
+        <v>3412.60659206992</v>
       </c>
       <c r="D14">
-        <v>3435.563141207244</v>
+        <v>3441.33659206992</v>
       </c>
       <c r="E14">
-        <v>-356.1800000000001</v>
+        <v>-316.77</v>
       </c>
       <c r="F14">
-        <v>472.92</v>
+        <v>512.33</v>
       </c>
       <c r="G14">
         <v>483.6</v>
@@ -2441,28 +2441,28 @@
         <v>298</v>
       </c>
       <c r="M14">
-        <v>24.497256</v>
+        <v>26.538694</v>
       </c>
       <c r="N14">
-        <v>273.502744</v>
+        <v>271.461306</v>
       </c>
       <c r="O14">
-        <v>54.70054880000001</v>
+        <v>54.2922612</v>
       </c>
       <c r="P14">
-        <v>218.8021952</v>
+        <v>217.1690448</v>
       </c>
       <c r="Q14">
-        <v>428.4021952</v>
+        <v>426.7690448</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09167212497608593</v>
+        <v>0.09210431006159644</v>
       </c>
       <c r="T14">
-        <v>0.9431791707564119</v>
+        <v>0.952065350997192</v>
       </c>
       <c r="U14">
         <v>0.0518</v>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>12.16462774442983</v>
+        <v>11.22888714870445</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.0855179497535889</v>
+        <v>0.0853916295282222</v>
       </c>
       <c r="C15">
-        <v>3412.60659206992</v>
+        <v>3378.989480121386</v>
       </c>
       <c r="D15">
-        <v>3441.33659206992</v>
+        <v>3447.129480121386</v>
       </c>
       <c r="E15">
-        <v>-316.77</v>
+        <v>-277.36</v>
       </c>
       <c r="F15">
-        <v>512.33</v>
+        <v>551.74</v>
       </c>
       <c r="G15">
         <v>483.6</v>
@@ -2523,28 +2523,28 @@
         <v>298</v>
       </c>
       <c r="M15">
-        <v>26.538694</v>
+        <v>28.580132</v>
       </c>
       <c r="N15">
-        <v>271.461306</v>
+        <v>269.419868</v>
       </c>
       <c r="O15">
-        <v>54.2922612</v>
+        <v>53.8839736</v>
       </c>
       <c r="P15">
-        <v>217.1690448</v>
+        <v>215.5358944</v>
       </c>
       <c r="Q15">
-        <v>426.7690448</v>
+        <v>425.1358944</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09210431006159644</v>
+        <v>0.09254654596304906</v>
       </c>
       <c r="T15">
-        <v>0.952065350997192</v>
+        <v>0.961158186592409</v>
       </c>
       <c r="U15">
         <v>0.0518</v>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>11.22888714870445</v>
+        <v>10.42682378093985</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.0853916295282222</v>
+        <v>0.08546930930285547</v>
       </c>
       <c r="C16">
-        <v>3378.989480121386</v>
+        <v>3336.014875893605</v>
       </c>
       <c r="D16">
-        <v>3447.129480121386</v>
+        <v>3443.564875893605</v>
       </c>
       <c r="E16">
-        <v>-277.36</v>
+        <v>-237.9499999999999</v>
       </c>
       <c r="F16">
-        <v>551.74</v>
+        <v>591.1500000000001</v>
       </c>
       <c r="G16">
         <v>483.6</v>
@@ -2605,45 +2605,45 @@
         <v>298</v>
       </c>
       <c r="M16">
-        <v>28.580132</v>
+        <v>31.626525</v>
       </c>
       <c r="N16">
-        <v>269.419868</v>
+        <v>266.373475</v>
       </c>
       <c r="O16">
-        <v>53.8839736</v>
+        <v>53.274695</v>
       </c>
       <c r="P16">
-        <v>215.5358944</v>
+        <v>213.09878</v>
       </c>
       <c r="Q16">
-        <v>425.1358944</v>
+        <v>422.6987799999999</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09254654596304906</v>
+        <v>0.09299918741512408</v>
       </c>
       <c r="T16">
-        <v>0.961158186592409</v>
+        <v>0.9704649712604546</v>
       </c>
       <c r="U16">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V16">
         <v>0.2</v>
       </c>
       <c r="W16">
-        <v>0.04144</v>
+        <v>0.0428</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y16">
-        <v>10.42682378093985</v>
+        <v>9.422470536993867</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08546930930285547</v>
+        <v>0.08535658907748876</v>
       </c>
       <c r="C17">
-        <v>3336.014875893605</v>
+        <v>3301.779848412914</v>
       </c>
       <c r="D17">
-        <v>3443.564875893605</v>
+        <v>3448.739848412914</v>
       </c>
       <c r="E17">
-        <v>-237.95</v>
+        <v>-198.54</v>
       </c>
       <c r="F17">
-        <v>591.15</v>
+        <v>630.5600000000001</v>
       </c>
       <c r="G17">
         <v>483.6</v>
@@ -2687,28 +2687,28 @@
         <v>298</v>
       </c>
       <c r="M17">
-        <v>31.626525</v>
+        <v>33.73496</v>
       </c>
       <c r="N17">
-        <v>266.373475</v>
+        <v>264.26504</v>
       </c>
       <c r="O17">
-        <v>53.274695</v>
+        <v>52.853008</v>
       </c>
       <c r="P17">
-        <v>213.09878</v>
+        <v>211.412032</v>
       </c>
       <c r="Q17">
-        <v>422.6987799999999</v>
+        <v>421.012032</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09299918741512408</v>
+        <v>0.09346260604462947</v>
       </c>
       <c r="T17">
-        <v>0.9704649712604546</v>
+        <v>0.9799933460396441</v>
       </c>
       <c r="U17">
         <v>0.0535</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>9.422470536993869</v>
+        <v>8.833566128431752</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08535658907748876</v>
+        <v>0.08524386885212205</v>
       </c>
       <c r="C18">
-        <v>3301.779848412914</v>
+        <v>3267.56039818863</v>
       </c>
       <c r="D18">
-        <v>3448.739848412914</v>
+        <v>3453.93039818863</v>
       </c>
       <c r="E18">
-        <v>-198.54</v>
+        <v>-159.13</v>
       </c>
       <c r="F18">
-        <v>630.5600000000001</v>
+        <v>669.97</v>
       </c>
       <c r="G18">
         <v>483.6</v>
@@ -2769,28 +2769,28 @@
         <v>298</v>
       </c>
       <c r="M18">
-        <v>33.73496</v>
+        <v>35.843395</v>
       </c>
       <c r="N18">
-        <v>264.26504</v>
+        <v>262.156605</v>
       </c>
       <c r="O18">
-        <v>52.853008</v>
+        <v>52.431321</v>
       </c>
       <c r="P18">
-        <v>211.412032</v>
+        <v>209.725284</v>
       </c>
       <c r="Q18">
-        <v>421.012032</v>
+        <v>419.325284</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09346260604462947</v>
+        <v>0.09393719138809886</v>
       </c>
       <c r="T18">
-        <v>0.9799933460396441</v>
+        <v>0.9897513202111032</v>
       </c>
       <c r="U18">
         <v>0.0535</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>8.833566128431752</v>
+        <v>8.313944591465178</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08524386885212205</v>
+        <v>0.08513114862675535</v>
       </c>
       <c r="C19">
-        <v>3267.56039818863</v>
+        <v>3233.356595660741</v>
       </c>
       <c r="D19">
-        <v>3453.93039818863</v>
+        <v>3459.136595660741</v>
       </c>
       <c r="E19">
-        <v>-159.13</v>
+        <v>-119.7199999999999</v>
       </c>
       <c r="F19">
-        <v>669.97</v>
+        <v>709.3800000000001</v>
       </c>
       <c r="G19">
         <v>483.6</v>
@@ -2851,28 +2851,28 @@
         <v>298</v>
       </c>
       <c r="M19">
-        <v>35.843395</v>
+        <v>37.95183000000001</v>
       </c>
       <c r="N19">
-        <v>262.156605</v>
+        <v>260.04817</v>
       </c>
       <c r="O19">
-        <v>52.431321</v>
+        <v>52.009634</v>
       </c>
       <c r="P19">
-        <v>209.725284</v>
+        <v>208.038536</v>
       </c>
       <c r="Q19">
-        <v>419.325284</v>
+        <v>417.6385359999999</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09393719138809886</v>
+        <v>0.09442335198384799</v>
       </c>
       <c r="T19">
-        <v>0.9897513202111032</v>
+        <v>0.9997472937525982</v>
       </c>
       <c r="U19">
         <v>0.0535</v>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>8.313944591465178</v>
+        <v>7.852058780828221</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08513114862675535</v>
+        <v>0.08514002840138862</v>
       </c>
       <c r="C20">
-        <v>3233.356595660741</v>
+        <v>3193.535896990971</v>
       </c>
       <c r="D20">
-        <v>3459.136595660741</v>
+        <v>3458.725896990971</v>
       </c>
       <c r="E20">
-        <v>-119.72</v>
+        <v>-80.31000000000006</v>
       </c>
       <c r="F20">
-        <v>709.38</v>
+        <v>748.79</v>
       </c>
       <c r="G20">
         <v>483.6</v>
@@ -2933,45 +2933,45 @@
         <v>298</v>
       </c>
       <c r="M20">
-        <v>37.95183</v>
+        <v>40.659297</v>
       </c>
       <c r="N20">
-        <v>260.04817</v>
+        <v>257.340703</v>
       </c>
       <c r="O20">
-        <v>52.00963400000001</v>
+        <v>51.46814060000001</v>
       </c>
       <c r="P20">
-        <v>208.038536</v>
+        <v>205.8725624</v>
       </c>
       <c r="Q20">
-        <v>417.638536</v>
+        <v>415.4725624</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09442335198384796</v>
+        <v>0.09492151654492423</v>
       </c>
       <c r="T20">
-        <v>0.999747293752598</v>
+        <v>1.009990081455611</v>
       </c>
       <c r="U20">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V20">
         <v>0.2</v>
       </c>
       <c r="W20">
-        <v>0.0428</v>
+        <v>0.04344000000000001</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y20">
-        <v>7.852058780828224</v>
+        <v>7.32919705916214</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08514002840138862</v>
+        <v>0.08503370817602193</v>
       </c>
       <c r="C21">
-        <v>3193.535896990971</v>
+        <v>3159.049732045384</v>
       </c>
       <c r="D21">
-        <v>3458.725896990971</v>
+        <v>3463.649732045385</v>
       </c>
       <c r="E21">
-        <v>-80.31000000000006</v>
+        <v>-40.89999999999998</v>
       </c>
       <c r="F21">
-        <v>748.79</v>
+        <v>788.2</v>
       </c>
       <c r="G21">
         <v>483.6</v>
@@ -3015,28 +3015,28 @@
         <v>298</v>
       </c>
       <c r="M21">
-        <v>40.659297</v>
+        <v>42.79926</v>
       </c>
       <c r="N21">
-        <v>257.340703</v>
+        <v>255.20074</v>
       </c>
       <c r="O21">
-        <v>51.46814060000001</v>
+        <v>51.040148</v>
       </c>
       <c r="P21">
-        <v>205.8725624</v>
+        <v>204.160592</v>
       </c>
       <c r="Q21">
-        <v>415.4725624</v>
+        <v>413.760592</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09492151654492423</v>
+        <v>0.0954321352200274</v>
       </c>
       <c r="T21">
-        <v>1.009990081455611</v>
+        <v>1.0204889388512</v>
       </c>
       <c r="U21">
         <v>0.0543</v>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>7.32919705916214</v>
+        <v>6.962737206204032</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08503370817602193</v>
+        <v>0.08492738795065521</v>
       </c>
       <c r="C22">
-        <v>3159.049732045384</v>
+        <v>3124.577606208704</v>
       </c>
       <c r="D22">
-        <v>3463.649732045385</v>
+        <v>3468.587606208705</v>
       </c>
       <c r="E22">
-        <v>-40.89999999999998</v>
+        <v>-1.489999999999895</v>
       </c>
       <c r="F22">
-        <v>788.2</v>
+        <v>827.6100000000001</v>
       </c>
       <c r="G22">
         <v>483.6</v>
@@ -3097,28 +3097,28 @@
         <v>298</v>
       </c>
       <c r="M22">
-        <v>42.79926</v>
+        <v>44.93922300000001</v>
       </c>
       <c r="N22">
-        <v>255.20074</v>
+        <v>253.060777</v>
       </c>
       <c r="O22">
-        <v>51.040148</v>
+        <v>50.61215540000001</v>
       </c>
       <c r="P22">
-        <v>204.160592</v>
+        <v>202.4486216</v>
       </c>
       <c r="Q22">
-        <v>413.760592</v>
+        <v>412.0486216</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.0954321352200274</v>
+        <v>0.09595568095019646</v>
       </c>
       <c r="T22">
-        <v>1.0204889388512</v>
+        <v>1.031253590104904</v>
       </c>
       <c r="U22">
         <v>0.0543</v>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>6.962737206204032</v>
+        <v>6.631178291622888</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08492738795065521</v>
+        <v>0.0848210677252885</v>
       </c>
       <c r="C23">
-        <v>3124.577606208704</v>
+        <v>3090.11957961027</v>
       </c>
       <c r="D23">
-        <v>3468.587606208705</v>
+        <v>3473.53957961027</v>
       </c>
       <c r="E23">
-        <v>-1.490000000000009</v>
+        <v>37.91999999999996</v>
       </c>
       <c r="F23">
-        <v>827.61</v>
+        <v>867.02</v>
       </c>
       <c r="G23">
         <v>483.6</v>
@@ -3179,28 +3179,28 @@
         <v>298</v>
       </c>
       <c r="M23">
-        <v>44.939223</v>
+        <v>47.079186</v>
       </c>
       <c r="N23">
-        <v>253.060777</v>
+        <v>250.920814</v>
       </c>
       <c r="O23">
-        <v>50.61215540000001</v>
+        <v>50.1841628</v>
       </c>
       <c r="P23">
-        <v>202.4486216</v>
+        <v>200.7366512</v>
       </c>
       <c r="Q23">
-        <v>412.0486216</v>
+        <v>410.3366512</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09595568095019646</v>
+        <v>0.09649265092985704</v>
       </c>
       <c r="T23">
-        <v>1.031253590104904</v>
+        <v>1.042294258057422</v>
       </c>
       <c r="U23">
         <v>0.0543</v>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>6.631178291622889</v>
+        <v>6.32976109654912</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.0848210677252885</v>
+        <v>0.08489874749992178</v>
       </c>
       <c r="C24">
-        <v>3090.11957961027</v>
+        <v>3047.090174562707</v>
       </c>
       <c r="D24">
-        <v>3473.53957961027</v>
+        <v>3469.920174562707</v>
       </c>
       <c r="E24">
-        <v>37.91999999999996</v>
+        <v>77.33000000000004</v>
       </c>
       <c r="F24">
-        <v>867.02</v>
+        <v>906.4300000000001</v>
       </c>
       <c r="G24">
         <v>483.6</v>
@@ -3261,45 +3261,45 @@
         <v>298</v>
       </c>
       <c r="M24">
-        <v>47.079186</v>
+        <v>50.125579</v>
       </c>
       <c r="N24">
-        <v>250.920814</v>
+        <v>247.874421</v>
       </c>
       <c r="O24">
-        <v>50.1841628</v>
+        <v>49.5748842</v>
       </c>
       <c r="P24">
-        <v>200.7366512</v>
+        <v>198.2995368</v>
       </c>
       <c r="Q24">
-        <v>410.3366512</v>
+        <v>407.8995368</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09649265092985704</v>
+        <v>0.09704356818171661</v>
       </c>
       <c r="T24">
-        <v>1.042294258057422</v>
+        <v>1.053621696606109</v>
       </c>
       <c r="U24">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V24">
         <v>0.2</v>
       </c>
       <c r="W24">
-        <v>0.04344000000000001</v>
+        <v>0.04424</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y24">
-        <v>6.32976109654912</v>
+        <v>5.945068484894708</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08489874749992178</v>
+        <v>0.08480042727455507</v>
       </c>
       <c r="C25">
-        <v>3047.090174562707</v>
+        <v>3012.262569130421</v>
       </c>
       <c r="D25">
-        <v>3469.920174562707</v>
+        <v>3474.502569130421</v>
       </c>
       <c r="E25">
-        <v>77.33000000000004</v>
+        <v>116.74</v>
       </c>
       <c r="F25">
-        <v>906.4300000000001</v>
+        <v>945.84</v>
       </c>
       <c r="G25">
         <v>483.6</v>
@@ -3343,28 +3343,28 @@
         <v>298</v>
       </c>
       <c r="M25">
-        <v>50.125579</v>
+        <v>52.304952</v>
       </c>
       <c r="N25">
-        <v>247.874421</v>
+        <v>245.695048</v>
       </c>
       <c r="O25">
-        <v>49.5748842</v>
+        <v>49.1390096</v>
       </c>
       <c r="P25">
-        <v>198.2995368</v>
+        <v>196.5560384</v>
       </c>
       <c r="Q25">
-        <v>407.8995368</v>
+        <v>406.1560383999999</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09704356818171661</v>
+        <v>0.09760898325599351</v>
       </c>
       <c r="T25">
-        <v>1.053621696606109</v>
+        <v>1.065247225642919</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.945068484894708</v>
+        <v>5.697357298024095</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08480042727455507</v>
+        <v>0.08470210704918836</v>
       </c>
       <c r="C26">
-        <v>3012.262569130421</v>
+        <v>2977.44708277068</v>
       </c>
       <c r="D26">
-        <v>3474.502569130421</v>
+        <v>3479.09708277068</v>
       </c>
       <c r="E26">
-        <v>116.7399999999999</v>
+        <v>156.15</v>
       </c>
       <c r="F26">
-        <v>945.8399999999999</v>
+        <v>985.25</v>
       </c>
       <c r="G26">
         <v>483.6</v>
@@ -3425,28 +3425,28 @@
         <v>298</v>
       </c>
       <c r="M26">
-        <v>52.304952</v>
+        <v>54.48432500000001</v>
       </c>
       <c r="N26">
-        <v>245.695048</v>
+        <v>243.515675</v>
       </c>
       <c r="O26">
-        <v>49.1390096</v>
+        <v>48.703135</v>
       </c>
       <c r="P26">
-        <v>196.5560384</v>
+        <v>194.81254</v>
       </c>
       <c r="Q26">
-        <v>406.1560383999999</v>
+        <v>404.41254</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.0976089832559935</v>
+        <v>0.09818947606558448</v>
       </c>
       <c r="T26">
-        <v>1.065247225642919</v>
+        <v>1.077182768787377</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.697357298024095</v>
+        <v>5.469463006103131</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08470210704918836</v>
+        <v>0.08460378682382164</v>
       </c>
       <c r="C27">
-        <v>2977.44708277068</v>
+        <v>2942.643763624164</v>
       </c>
       <c r="D27">
-        <v>3479.09708277068</v>
+        <v>3483.703763624163</v>
       </c>
       <c r="E27">
-        <v>156.15</v>
+        <v>195.5600000000001</v>
       </c>
       <c r="F27">
-        <v>985.25</v>
+        <v>1024.66</v>
       </c>
       <c r="G27">
         <v>483.6</v>
@@ -3507,28 +3507,28 @@
         <v>298</v>
       </c>
       <c r="M27">
-        <v>54.48432500000001</v>
+        <v>56.663698</v>
       </c>
       <c r="N27">
-        <v>243.515675</v>
+        <v>241.336302</v>
       </c>
       <c r="O27">
-        <v>48.703135</v>
+        <v>48.2672604</v>
       </c>
       <c r="P27">
-        <v>194.81254</v>
+        <v>193.0690416</v>
       </c>
       <c r="Q27">
-        <v>404.41254</v>
+        <v>402.6690416</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09818947606558448</v>
+        <v>0.09878565787002924</v>
       </c>
       <c r="T27">
-        <v>1.077182768787377</v>
+        <v>1.089440894178983</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.469463006103131</v>
+        <v>5.259099044329933</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08460378682382164</v>
+        <v>0.08450546659845494</v>
       </c>
       <c r="C28">
-        <v>2942.643763624164</v>
+        <v>2907.852660086862</v>
       </c>
       <c r="D28">
-        <v>3483.703763624163</v>
+        <v>3488.322660086862</v>
       </c>
       <c r="E28">
-        <v>195.5600000000001</v>
+        <v>234.9700000000001</v>
       </c>
       <c r="F28">
-        <v>1024.66</v>
+        <v>1064.07</v>
       </c>
       <c r="G28">
         <v>483.6</v>
@@ -3589,28 +3589,28 @@
         <v>298</v>
       </c>
       <c r="M28">
-        <v>56.663698</v>
+        <v>58.84307100000001</v>
       </c>
       <c r="N28">
-        <v>241.336302</v>
+        <v>239.156929</v>
       </c>
       <c r="O28">
-        <v>48.2672604</v>
+        <v>47.8313858</v>
       </c>
       <c r="P28">
-        <v>193.0690416</v>
+        <v>191.3255432</v>
       </c>
       <c r="Q28">
-        <v>402.6690416</v>
+        <v>400.9255432</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09878565787002924</v>
+        <v>0.09939817342254101</v>
       </c>
       <c r="T28">
-        <v>1.089440894178983</v>
+        <v>1.102034858622414</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.259099044329933</v>
+        <v>5.064317598243639</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08450546659845494</v>
+        <v>0.08440714637308822</v>
       </c>
       <c r="C29">
-        <v>2907.852660086862</v>
+        <v>2873.073820811772</v>
       </c>
       <c r="D29">
-        <v>3488.322660086862</v>
+        <v>3492.953820811772</v>
       </c>
       <c r="E29">
-        <v>234.9700000000001</v>
+        <v>274.38</v>
       </c>
       <c r="F29">
-        <v>1064.07</v>
+        <v>1103.48</v>
       </c>
       <c r="G29">
         <v>483.6</v>
@@ -3671,28 +3671,28 @@
         <v>298</v>
       </c>
       <c r="M29">
-        <v>58.84307100000001</v>
+        <v>61.022444</v>
       </c>
       <c r="N29">
-        <v>239.156929</v>
+        <v>236.977556</v>
       </c>
       <c r="O29">
-        <v>47.8313858</v>
+        <v>47.3955112</v>
       </c>
       <c r="P29">
-        <v>191.3255432</v>
+        <v>189.5820448</v>
       </c>
       <c r="Q29">
-        <v>400.9255432</v>
+        <v>399.1820448</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09939817342254101</v>
+        <v>0.1000277032959559</v>
       </c>
       <c r="T29">
-        <v>1.102034858622414</v>
+        <v>1.114978655411496</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>5.064317598243639</v>
+        <v>4.883449112592082</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08440714637308822</v>
+        <v>0.08430882614772149</v>
       </c>
       <c r="C30">
-        <v>2873.073820811772</v>
+        <v>2838.307294710604</v>
       </c>
       <c r="D30">
-        <v>3492.953820811772</v>
+        <v>3497.597294710604</v>
       </c>
       <c r="E30">
-        <v>274.38</v>
+        <v>313.7900000000001</v>
       </c>
       <c r="F30">
-        <v>1103.48</v>
+        <v>1142.89</v>
       </c>
       <c r="G30">
         <v>483.6</v>
@@ -3753,28 +3753,28 @@
         <v>298</v>
       </c>
       <c r="M30">
-        <v>61.022444</v>
+        <v>63.20181700000001</v>
       </c>
       <c r="N30">
-        <v>236.977556</v>
+        <v>234.798183</v>
       </c>
       <c r="O30">
-        <v>47.3955112</v>
+        <v>46.9596366</v>
       </c>
       <c r="P30">
-        <v>189.5820448</v>
+        <v>187.8385464</v>
       </c>
       <c r="Q30">
-        <v>399.1820448</v>
+        <v>397.4385464</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1000277032959559</v>
+        <v>0.1006749664052416</v>
       </c>
       <c r="T30">
-        <v>1.114978655411496</v>
+        <v>1.128287066194636</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>4.883449112592082</v>
+        <v>4.715054315606148</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08430882614772149</v>
+        <v>0.08421050592235479</v>
       </c>
       <c r="C31">
-        <v>2838.307294710604</v>
+        <v>2803.553130955502</v>
       </c>
       <c r="D31">
-        <v>3497.597294710604</v>
+        <v>3502.253130955502</v>
       </c>
       <c r="E31">
-        <v>313.7899999999998</v>
+        <v>353.1999999999999</v>
       </c>
       <c r="F31">
-        <v>1142.89</v>
+        <v>1182.3</v>
       </c>
       <c r="G31">
         <v>483.6</v>
@@ -3835,28 +3835,28 @@
         <v>298</v>
       </c>
       <c r="M31">
-        <v>63.201817</v>
+        <v>65.38119</v>
       </c>
       <c r="N31">
-        <v>234.798183</v>
+        <v>232.61881</v>
       </c>
       <c r="O31">
-        <v>46.9596366</v>
+        <v>46.523762</v>
       </c>
       <c r="P31">
-        <v>187.8385464</v>
+        <v>186.095048</v>
       </c>
       <c r="Q31">
-        <v>397.4385464</v>
+        <v>395.695048</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1006749664052416</v>
+        <v>0.1013407227462211</v>
       </c>
       <c r="T31">
-        <v>1.128287066194636</v>
+        <v>1.141975717285866</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>4.715054315606148</v>
+        <v>4.557885838419276</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08421050592235479</v>
+        <v>0.08473218569698808</v>
       </c>
       <c r="C32">
-        <v>2803.553130955502</v>
+        <v>2739.580215117071</v>
       </c>
       <c r="D32">
-        <v>3502.253130955502</v>
+        <v>3477.690215117071</v>
       </c>
       <c r="E32">
-        <v>353.1999999999999</v>
+        <v>392.61</v>
       </c>
       <c r="F32">
-        <v>1182.3</v>
+        <v>1221.71</v>
       </c>
       <c r="G32">
         <v>483.6</v>
@@ -3917,45 +3917,45 @@
         <v>298</v>
       </c>
       <c r="M32">
-        <v>65.38119</v>
+        <v>70.61483800000001</v>
       </c>
       <c r="N32">
-        <v>232.61881</v>
+        <v>227.385162</v>
       </c>
       <c r="O32">
-        <v>46.523762</v>
+        <v>45.4770324</v>
       </c>
       <c r="P32">
-        <v>186.095048</v>
+        <v>181.9081296</v>
       </c>
       <c r="Q32">
-        <v>395.695048</v>
+        <v>391.5081296</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1013407227462211</v>
+        <v>0.1020257763724465</v>
       </c>
       <c r="T32">
-        <v>1.141975717285866</v>
+        <v>1.156061140872494</v>
       </c>
       <c r="U32">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V32">
         <v>0.2</v>
       </c>
       <c r="W32">
-        <v>0.04424</v>
+        <v>0.04624</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y32">
-        <v>4.557885838419276</v>
+        <v>4.220076239500825</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08473218569698808</v>
+        <v>0.08465386547162138</v>
       </c>
       <c r="C33">
-        <v>2739.580215117071</v>
+        <v>2703.835862923534</v>
       </c>
       <c r="D33">
-        <v>3477.690215117071</v>
+        <v>3481.355862923534</v>
       </c>
       <c r="E33">
-        <v>392.61</v>
+        <v>432.0200000000001</v>
       </c>
       <c r="F33">
-        <v>1221.71</v>
+        <v>1261.12</v>
       </c>
       <c r="G33">
         <v>483.6</v>
@@ -3999,28 +3999,28 @@
         <v>298</v>
       </c>
       <c r="M33">
-        <v>70.61483800000001</v>
+        <v>72.89273600000001</v>
       </c>
       <c r="N33">
-        <v>227.385162</v>
+        <v>225.107264</v>
       </c>
       <c r="O33">
-        <v>45.4770324</v>
+        <v>45.0214528</v>
       </c>
       <c r="P33">
-        <v>181.9081296</v>
+        <v>180.0858112</v>
       </c>
       <c r="Q33">
-        <v>391.5081296</v>
+        <v>389.6858112</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1020257763724465</v>
+        <v>0.1027309786347373</v>
       </c>
       <c r="T33">
-        <v>1.156061140872494</v>
+        <v>1.170560841623435</v>
       </c>
       <c r="U33">
         <v>0.0578</v>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>4.220076239500825</v>
+        <v>4.088198857016424</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08465386547162138</v>
+        <v>0.08549954524625467</v>
       </c>
       <c r="C34">
-        <v>2703.835862923534</v>
+        <v>2625.249387832647</v>
       </c>
       <c r="D34">
-        <v>3481.355862923534</v>
+        <v>3442.179387832647</v>
       </c>
       <c r="E34">
-        <v>432.0200000000001</v>
+        <v>471.4299999999999</v>
       </c>
       <c r="F34">
-        <v>1261.12</v>
+        <v>1300.53</v>
       </c>
       <c r="G34">
         <v>483.6</v>
@@ -4081,45 +4081,45 @@
         <v>298</v>
       </c>
       <c r="M34">
-        <v>72.89273600000001</v>
+        <v>79.722489</v>
       </c>
       <c r="N34">
-        <v>225.107264</v>
+        <v>218.277511</v>
       </c>
       <c r="O34">
-        <v>45.0214528</v>
+        <v>43.6555022</v>
       </c>
       <c r="P34">
-        <v>180.0858112</v>
+        <v>174.6220088</v>
       </c>
       <c r="Q34">
-        <v>389.6858112</v>
+        <v>384.2220088</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1027309786347373</v>
+        <v>0.1034572317108279</v>
       </c>
       <c r="T34">
-        <v>1.170560841623435</v>
+        <v>1.185493369262463</v>
       </c>
       <c r="U34">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V34">
         <v>0.2</v>
       </c>
       <c r="W34">
-        <v>0.04624</v>
+        <v>0.04904</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y34">
-        <v>4.088198857016424</v>
+        <v>3.737966585564081</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08549954524625467</v>
+        <v>0.08544922502088793</v>
       </c>
       <c r="C35">
-        <v>2625.249387832647</v>
+        <v>2588.145805581892</v>
       </c>
       <c r="D35">
-        <v>3442.179387832647</v>
+        <v>3444.485805581892</v>
       </c>
       <c r="E35">
-        <v>471.4299999999999</v>
+        <v>510.84</v>
       </c>
       <c r="F35">
-        <v>1300.53</v>
+        <v>1339.94</v>
       </c>
       <c r="G35">
         <v>483.6</v>
@@ -4163,28 +4163,28 @@
         <v>298</v>
       </c>
       <c r="M35">
-        <v>79.722489</v>
+        <v>82.138322</v>
       </c>
       <c r="N35">
-        <v>218.277511</v>
+        <v>215.861678</v>
       </c>
       <c r="O35">
-        <v>43.6555022</v>
+        <v>43.1723356</v>
       </c>
       <c r="P35">
-        <v>174.6220088</v>
+        <v>172.6893424</v>
       </c>
       <c r="Q35">
-        <v>384.2220088</v>
+        <v>382.2893424</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1034572317108279</v>
+        <v>0.1042054924558908</v>
       </c>
       <c r="T35">
-        <v>1.185493369262463</v>
+        <v>1.200878397739038</v>
       </c>
       <c r="U35">
         <v>0.0613</v>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.737966585564081</v>
+        <v>3.628026391871019</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08544922502088793</v>
+        <v>0.08539890479552123</v>
       </c>
       <c r="C36">
-        <v>2588.145805581892</v>
+        <v>2551.045316214438</v>
       </c>
       <c r="D36">
-        <v>3444.485805581892</v>
+        <v>3446.795316214438</v>
       </c>
       <c r="E36">
-        <v>510.84</v>
+        <v>550.2500000000001</v>
       </c>
       <c r="F36">
-        <v>1339.94</v>
+        <v>1379.35</v>
       </c>
       <c r="G36">
         <v>483.6</v>
@@ -4245,28 +4245,28 @@
         <v>298</v>
       </c>
       <c r="M36">
-        <v>82.138322</v>
+        <v>84.55415500000001</v>
       </c>
       <c r="N36">
-        <v>215.861678</v>
+        <v>213.445845</v>
       </c>
       <c r="O36">
-        <v>43.1723356</v>
+        <v>42.689169</v>
       </c>
       <c r="P36">
-        <v>172.6893424</v>
+        <v>170.756676</v>
       </c>
       <c r="Q36">
-        <v>382.2893424</v>
+        <v>380.356676</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1042054924558908</v>
+        <v>0.1049767766084942</v>
       </c>
       <c r="T36">
-        <v>1.200878397739038</v>
+        <v>1.2167368117072</v>
       </c>
       <c r="U36">
         <v>0.0613</v>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.628026391871019</v>
+        <v>3.524368494960419</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08539890479552123</v>
+        <v>0.08615498457015452</v>
       </c>
       <c r="C37">
-        <v>2551.045316214438</v>
+        <v>2477.25714853147</v>
       </c>
       <c r="D37">
-        <v>3446.795316214438</v>
+        <v>3412.417148531471</v>
       </c>
       <c r="E37">
-        <v>550.2500000000001</v>
+        <v>589.6600000000002</v>
       </c>
       <c r="F37">
-        <v>1379.35</v>
+        <v>1418.76</v>
       </c>
       <c r="G37">
         <v>483.6</v>
@@ -4327,45 +4327,45 @@
         <v>298</v>
       </c>
       <c r="M37">
-        <v>84.55415500000001</v>
+        <v>90.94251600000003</v>
       </c>
       <c r="N37">
-        <v>213.445845</v>
+        <v>207.057484</v>
       </c>
       <c r="O37">
-        <v>42.689169</v>
+        <v>41.4114968</v>
       </c>
       <c r="P37">
-        <v>170.756676</v>
+        <v>165.6459872</v>
       </c>
       <c r="Q37">
-        <v>380.356676</v>
+        <v>375.2459871999999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1049767766084942</v>
+        <v>0.1057721633908665</v>
       </c>
       <c r="T37">
-        <v>1.2167368117072</v>
+        <v>1.233090801111866</v>
       </c>
       <c r="U37">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V37">
         <v>0.2</v>
       </c>
       <c r="W37">
-        <v>0.04904</v>
+        <v>0.05128000000000001</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y37">
-        <v>3.524368494960419</v>
+        <v>3.276795201047659</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08615498457015451</v>
+        <v>0.08612706434478781</v>
       </c>
       <c r="C38">
-        <v>2477.257148531471</v>
+        <v>2439.10445350161</v>
       </c>
       <c r="D38">
-        <v>3412.417148531471</v>
+        <v>3413.674453501611</v>
       </c>
       <c r="E38">
-        <v>589.66</v>
+        <v>629.0700000000001</v>
       </c>
       <c r="F38">
-        <v>1418.76</v>
+        <v>1458.17</v>
       </c>
       <c r="G38">
         <v>483.6</v>
@@ -4409,28 +4409,28 @@
         <v>298</v>
       </c>
       <c r="M38">
-        <v>90.94251600000001</v>
+        <v>93.46869700000001</v>
       </c>
       <c r="N38">
-        <v>207.057484</v>
+        <v>204.531303</v>
       </c>
       <c r="O38">
-        <v>41.4114968</v>
+        <v>40.9062606</v>
       </c>
       <c r="P38">
-        <v>165.6459872</v>
+        <v>163.6250424</v>
       </c>
       <c r="Q38">
-        <v>375.2459871999999</v>
+        <v>373.2250424</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1057721633908664</v>
+        <v>0.1065928005472822</v>
       </c>
       <c r="T38">
-        <v>1.233090801111866</v>
+        <v>1.249963964783348</v>
       </c>
       <c r="U38">
         <v>0.0641</v>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.276795201047659</v>
+        <v>3.188233168586912</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08612706434478781</v>
+        <v>0.08609914411942109</v>
       </c>
       <c r="C39">
-        <v>2439.10445350161</v>
+        <v>2400.952685321186</v>
       </c>
       <c r="D39">
-        <v>3413.674453501611</v>
+        <v>3414.932685321186</v>
       </c>
       <c r="E39">
-        <v>629.0700000000001</v>
+        <v>668.4799999999999</v>
       </c>
       <c r="F39">
-        <v>1458.17</v>
+        <v>1497.58</v>
       </c>
       <c r="G39">
         <v>483.6</v>
@@ -4491,28 +4491,28 @@
         <v>298</v>
       </c>
       <c r="M39">
-        <v>93.46869700000001</v>
+        <v>95.994878</v>
       </c>
       <c r="N39">
-        <v>204.531303</v>
+        <v>202.005122</v>
       </c>
       <c r="O39">
-        <v>40.9062606</v>
+        <v>40.4010244</v>
       </c>
       <c r="P39">
-        <v>163.6250424</v>
+        <v>161.6040976</v>
       </c>
       <c r="Q39">
-        <v>373.2250424</v>
+        <v>371.2040976</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1065928005472822</v>
+        <v>0.107439909870034</v>
       </c>
       <c r="T39">
-        <v>1.249963964783348</v>
+        <v>1.267381424057135</v>
       </c>
       <c r="U39">
         <v>0.0641</v>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.188233168586912</v>
+        <v>3.104332295729362</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08609914411942109</v>
+        <v>0.08607122389405439</v>
       </c>
       <c r="C40">
-        <v>2400.952685321186</v>
+        <v>2362.801845015445</v>
       </c>
       <c r="D40">
-        <v>3414.932685321186</v>
+        <v>3416.191845015445</v>
       </c>
       <c r="E40">
-        <v>668.4799999999999</v>
+        <v>707.89</v>
       </c>
       <c r="F40">
-        <v>1497.58</v>
+        <v>1536.99</v>
       </c>
       <c r="G40">
         <v>483.6</v>
@@ -4573,28 +4573,28 @@
         <v>298</v>
       </c>
       <c r="M40">
-        <v>95.994878</v>
+        <v>98.52105900000001</v>
       </c>
       <c r="N40">
-        <v>202.005122</v>
+        <v>199.478941</v>
       </c>
       <c r="O40">
-        <v>40.4010244</v>
+        <v>39.8957882</v>
       </c>
       <c r="P40">
-        <v>161.6040976</v>
+        <v>159.5831528</v>
       </c>
       <c r="Q40">
-        <v>371.2040976</v>
+        <v>369.1831528</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.107439909870034</v>
+        <v>0.1083147932689416</v>
       </c>
       <c r="T40">
-        <v>1.267381424057135</v>
+        <v>1.285369947569407</v>
       </c>
       <c r="U40">
         <v>0.0641</v>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>3.104332295729362</v>
+        <v>3.024734031736301</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08607122389405439</v>
+        <v>0.08853930366868766</v>
       </c>
       <c r="C41">
-        <v>2362.801845015445</v>
+        <v>2215.558878296321</v>
       </c>
       <c r="D41">
-        <v>3416.191845015445</v>
+        <v>3308.358878296321</v>
       </c>
       <c r="E41">
-        <v>707.89</v>
+        <v>747.3000000000001</v>
       </c>
       <c r="F41">
-        <v>1536.99</v>
+        <v>1576.4</v>
       </c>
       <c r="G41">
         <v>483.6</v>
@@ -4655,45 +4655,45 @@
         <v>298</v>
       </c>
       <c r="M41">
-        <v>98.52105900000001</v>
+        <v>113.34316</v>
       </c>
       <c r="N41">
-        <v>199.478941</v>
+        <v>184.65684</v>
       </c>
       <c r="O41">
-        <v>39.8957882</v>
+        <v>36.931368</v>
       </c>
       <c r="P41">
-        <v>159.5831528</v>
+        <v>147.725472</v>
       </c>
       <c r="Q41">
-        <v>369.1831528</v>
+        <v>357.325472</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1083147932689416</v>
+        <v>0.1092188394478128</v>
       </c>
       <c r="T41">
-        <v>1.285369947569407</v>
+        <v>1.303958088532088</v>
       </c>
       <c r="U41">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V41">
         <v>0.2</v>
       </c>
       <c r="W41">
-        <v>0.05128000000000001</v>
+        <v>0.05752000000000001</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y41">
-        <v>3.024734031736301</v>
+        <v>2.629183799004721</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08853930366868766</v>
+        <v>0.08857378344332098</v>
       </c>
       <c r="C42">
-        <v>2215.558878296321</v>
+        <v>2174.690615921337</v>
       </c>
       <c r="D42">
-        <v>3308.358878296321</v>
+        <v>3306.900615921337</v>
       </c>
       <c r="E42">
-        <v>747.3000000000001</v>
+        <v>786.7100000000002</v>
       </c>
       <c r="F42">
-        <v>1576.4</v>
+        <v>1615.81</v>
       </c>
       <c r="G42">
         <v>483.6</v>
@@ -4737,28 +4737,28 @@
         <v>298</v>
       </c>
       <c r="M42">
-        <v>113.34316</v>
+        <v>116.176739</v>
       </c>
       <c r="N42">
-        <v>184.65684</v>
+        <v>181.823261</v>
       </c>
       <c r="O42">
-        <v>36.931368</v>
+        <v>36.36465219999999</v>
       </c>
       <c r="P42">
-        <v>147.725472</v>
+        <v>145.4586088</v>
       </c>
       <c r="Q42">
-        <v>357.325472</v>
+        <v>355.0586088</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1092188394478128</v>
+        <v>0.110153531259866</v>
       </c>
       <c r="T42">
-        <v>1.303958088532088</v>
+        <v>1.323176335968081</v>
       </c>
       <c r="U42">
         <v>0.07190000000000001</v>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.629183799004721</v>
+        <v>2.565057364882655</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08857378344332098</v>
+        <v>0.08860826321795426</v>
       </c>
       <c r="C43">
-        <v>2174.690615921337</v>
+        <v>2133.823638529218</v>
       </c>
       <c r="D43">
-        <v>3306.900615921337</v>
+        <v>3305.443638529218</v>
       </c>
       <c r="E43">
-        <v>786.7100000000002</v>
+        <v>826.1200000000002</v>
       </c>
       <c r="F43">
-        <v>1615.81</v>
+        <v>1655.22</v>
       </c>
       <c r="G43">
         <v>483.6</v>
@@ -4819,28 +4819,28 @@
         <v>298</v>
       </c>
       <c r="M43">
-        <v>116.176739</v>
+        <v>119.010318</v>
       </c>
       <c r="N43">
-        <v>181.823261</v>
+        <v>178.989682</v>
       </c>
       <c r="O43">
-        <v>36.36465219999999</v>
+        <v>35.79793639999999</v>
       </c>
       <c r="P43">
-        <v>145.4586088</v>
+        <v>143.1917456</v>
       </c>
       <c r="Q43">
-        <v>355.0586088</v>
+        <v>352.7917456</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.110153531259866</v>
+        <v>0.1111204538240591</v>
       </c>
       <c r="T43">
-        <v>1.323176335968081</v>
+        <v>1.343057281591522</v>
       </c>
       <c r="U43">
         <v>0.07190000000000001</v>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.565057364882655</v>
+        <v>2.503984570480687</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08860826321795426</v>
+        <v>0.08998434299258755</v>
       </c>
       <c r="C44">
-        <v>2133.823638529218</v>
+        <v>2037.295970575331</v>
       </c>
       <c r="D44">
-        <v>3305.443638529218</v>
+        <v>3248.325970575331</v>
       </c>
       <c r="E44">
-        <v>826.12</v>
+        <v>865.5299999999999</v>
       </c>
       <c r="F44">
-        <v>1655.22</v>
+        <v>1694.63</v>
       </c>
       <c r="G44">
         <v>483.6</v>
@@ -4901,45 +4901,45 @@
         <v>298</v>
       </c>
       <c r="M44">
-        <v>119.010318</v>
+        <v>128.452954</v>
       </c>
       <c r="N44">
-        <v>178.989682</v>
+        <v>169.547046</v>
       </c>
       <c r="O44">
-        <v>35.7979364</v>
+        <v>33.9094092</v>
       </c>
       <c r="P44">
-        <v>143.1917456</v>
+        <v>135.6376368</v>
       </c>
       <c r="Q44">
-        <v>352.7917456</v>
+        <v>345.2376368</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1111204538240591</v>
+        <v>0.1121213034957676</v>
       </c>
       <c r="T44">
-        <v>1.343057281591521</v>
+        <v>1.363635804254381</v>
       </c>
       <c r="U44">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V44">
         <v>0.2</v>
       </c>
       <c r="W44">
-        <v>0.05752000000000001</v>
+        <v>0.06064000000000001</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y44">
-        <v>2.503984570480687</v>
+        <v>2.319915507743014</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08998434299258755</v>
+        <v>0.09005002276722082</v>
       </c>
       <c r="C45">
-        <v>2037.295970575331</v>
+        <v>1995.209081868316</v>
       </c>
       <c r="D45">
-        <v>3248.325970575331</v>
+        <v>3245.649081868316</v>
       </c>
       <c r="E45">
-        <v>865.5299999999999</v>
+        <v>904.9399999999999</v>
       </c>
       <c r="F45">
-        <v>1694.63</v>
+        <v>1734.04</v>
       </c>
       <c r="G45">
         <v>483.6</v>
@@ -4983,28 +4983,28 @@
         <v>298</v>
       </c>
       <c r="M45">
-        <v>128.452954</v>
+        <v>131.440232</v>
       </c>
       <c r="N45">
-        <v>169.547046</v>
+        <v>166.559768</v>
       </c>
       <c r="O45">
-        <v>33.9094092</v>
+        <v>33.3119536</v>
       </c>
       <c r="P45">
-        <v>135.6376368</v>
+        <v>133.2478144</v>
       </c>
       <c r="Q45">
-        <v>345.2376368</v>
+        <v>342.8478143999999</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1121213034957676</v>
+        <v>0.1131578977986086</v>
       </c>
       <c r="T45">
-        <v>1.363635804254381</v>
+        <v>1.3849492741552</v>
       </c>
       <c r="U45">
         <v>0.07580000000000001</v>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.319915507743014</v>
+        <v>2.267190155294309</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09005002276722082</v>
+        <v>0.09011570254185411</v>
       </c>
       <c r="C46">
-        <v>1995.209081868316</v>
+        <v>1953.126601482954</v>
       </c>
       <c r="D46">
-        <v>3245.649081868316</v>
+        <v>3242.976601482954</v>
       </c>
       <c r="E46">
-        <v>904.9399999999999</v>
+        <v>944.35</v>
       </c>
       <c r="F46">
-        <v>1734.04</v>
+        <v>1773.45</v>
       </c>
       <c r="G46">
         <v>483.6</v>
@@ -5065,28 +5065,28 @@
         <v>298</v>
       </c>
       <c r="M46">
-        <v>131.440232</v>
+        <v>134.42751</v>
       </c>
       <c r="N46">
-        <v>166.559768</v>
+        <v>163.57249</v>
       </c>
       <c r="O46">
-        <v>33.3119536</v>
+        <v>32.714498</v>
       </c>
       <c r="P46">
-        <v>133.2478144</v>
+        <v>130.857992</v>
       </c>
       <c r="Q46">
-        <v>342.8478143999999</v>
+        <v>340.457992</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1131578977986086</v>
+        <v>0.1142321864397347</v>
       </c>
       <c r="T46">
-        <v>1.3849492741552</v>
+        <v>1.407037779325139</v>
       </c>
       <c r="U46">
         <v>0.07580000000000001</v>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.267190155294309</v>
+        <v>2.216808151843324</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09011570254185411</v>
+        <v>0.0901813823164874</v>
       </c>
       <c r="C47">
-        <v>1953.126601482954</v>
+        <v>1911.048518538715</v>
       </c>
       <c r="D47">
-        <v>3242.976601482954</v>
+        <v>3240.308518538715</v>
       </c>
       <c r="E47">
-        <v>944.35</v>
+        <v>983.7600000000001</v>
       </c>
       <c r="F47">
-        <v>1773.45</v>
+        <v>1812.86</v>
       </c>
       <c r="G47">
         <v>483.6</v>
@@ -5147,28 +5147,28 @@
         <v>298</v>
       </c>
       <c r="M47">
-        <v>134.42751</v>
+        <v>137.414788</v>
       </c>
       <c r="N47">
-        <v>163.57249</v>
+        <v>160.585212</v>
       </c>
       <c r="O47">
-        <v>32.714498</v>
+        <v>32.1170424</v>
       </c>
       <c r="P47">
-        <v>130.857992</v>
+        <v>128.4681696</v>
       </c>
       <c r="Q47">
-        <v>340.457992</v>
+        <v>338.0681696</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1142321864397347</v>
+        <v>0.1153462635490507</v>
       </c>
       <c r="T47">
-        <v>1.407037779325139</v>
+        <v>1.42994437727915</v>
       </c>
       <c r="U47">
         <v>0.07580000000000001</v>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.216808151843324</v>
+        <v>2.168616670281513</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.0901813823164874</v>
+        <v>0.09024706209112068</v>
       </c>
       <c r="C48">
-        <v>1911.048518538715</v>
+        <v>1868.974822190848</v>
       </c>
       <c r="D48">
-        <v>3240.308518538715</v>
+        <v>3237.644822190848</v>
       </c>
       <c r="E48">
-        <v>983.7600000000001</v>
+        <v>1023.17</v>
       </c>
       <c r="F48">
-        <v>1812.86</v>
+        <v>1852.27</v>
       </c>
       <c r="G48">
         <v>483.6</v>
@@ -5229,28 +5229,28 @@
         <v>298</v>
       </c>
       <c r="M48">
-        <v>137.414788</v>
+        <v>140.402066</v>
       </c>
       <c r="N48">
-        <v>160.585212</v>
+        <v>157.597934</v>
       </c>
       <c r="O48">
-        <v>32.1170424</v>
+        <v>31.5195868</v>
       </c>
       <c r="P48">
-        <v>128.4681696</v>
+        <v>126.0783472</v>
       </c>
       <c r="Q48">
-        <v>338.0681696</v>
+        <v>335.6783472</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1153462635490507</v>
+        <v>0.1165023813040013</v>
       </c>
       <c r="T48">
-        <v>1.42994437727915</v>
+        <v>1.453715375155954</v>
       </c>
       <c r="U48">
         <v>0.07580000000000001</v>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.168616670281513</v>
+        <v>2.122475890062757</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09024706209112068</v>
+        <v>0.09031274186575398</v>
       </c>
       <c r="C49">
-        <v>1868.974822190848</v>
+        <v>1826.905501630229</v>
       </c>
       <c r="D49">
-        <v>3237.644822190848</v>
+        <v>3234.985501630229</v>
       </c>
       <c r="E49">
-        <v>1023.17</v>
+        <v>1062.58</v>
       </c>
       <c r="F49">
-        <v>1852.27</v>
+        <v>1891.68</v>
       </c>
       <c r="G49">
         <v>483.6</v>
@@ -5311,28 +5311,28 @@
         <v>298</v>
       </c>
       <c r="M49">
-        <v>140.402066</v>
+        <v>143.389344</v>
       </c>
       <c r="N49">
-        <v>157.597934</v>
+        <v>154.610656</v>
       </c>
       <c r="O49">
-        <v>31.5195868</v>
+        <v>30.9221312</v>
       </c>
       <c r="P49">
-        <v>126.0783472</v>
+        <v>123.6885248</v>
       </c>
       <c r="Q49">
-        <v>335.6783472</v>
+        <v>333.2885248</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1165023813040013</v>
+        <v>0.11770296512645</v>
       </c>
       <c r="T49">
-        <v>1.453715375155954</v>
+        <v>1.478400642181866</v>
       </c>
       <c r="U49">
         <v>0.07580000000000001</v>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.122475890062757</v>
+        <v>2.078257642353116</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09031274186575398</v>
+        <v>0.09037842164038727</v>
       </c>
       <c r="C50">
-        <v>1826.90550163023</v>
+        <v>1784.840546083223</v>
       </c>
       <c r="D50">
-        <v>3234.985501630229</v>
+        <v>3232.330546083223</v>
       </c>
       <c r="E50">
-        <v>1062.58</v>
+        <v>1101.99</v>
       </c>
       <c r="F50">
-        <v>1891.68</v>
+        <v>1931.09</v>
       </c>
       <c r="G50">
         <v>483.6</v>
@@ -5393,28 +5393,28 @@
         <v>298</v>
       </c>
       <c r="M50">
-        <v>143.389344</v>
+        <v>146.376622</v>
       </c>
       <c r="N50">
-        <v>154.610656</v>
+        <v>151.623378</v>
       </c>
       <c r="O50">
-        <v>30.9221312</v>
+        <v>30.3246756</v>
       </c>
       <c r="P50">
-        <v>123.6885248</v>
+        <v>121.2987024</v>
       </c>
       <c r="Q50">
-        <v>333.2885248</v>
+        <v>330.8987024</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.11770296512645</v>
+        <v>0.118950630667426</v>
       </c>
       <c r="T50">
-        <v>1.478400642181866</v>
+        <v>1.504053958895069</v>
       </c>
       <c r="U50">
         <v>0.07580000000000001</v>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.078257642353117</v>
+        <v>2.035844221080604</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09037842164038727</v>
+        <v>0.09612410141502054</v>
       </c>
       <c r="C51">
-        <v>1784.840546083223</v>
+        <v>1528.910212925408</v>
       </c>
       <c r="D51">
-        <v>3232.330546083223</v>
+        <v>3015.810212925408</v>
       </c>
       <c r="E51">
-        <v>1101.99</v>
+        <v>1141.4</v>
       </c>
       <c r="F51">
-        <v>1931.09</v>
+        <v>1970.5</v>
       </c>
       <c r="G51">
         <v>483.6</v>
@@ -5475,45 +5475,45 @@
         <v>298</v>
       </c>
       <c r="M51">
-        <v>146.376622</v>
+        <v>177.345</v>
       </c>
       <c r="N51">
-        <v>151.623378</v>
+        <v>120.655</v>
       </c>
       <c r="O51">
-        <v>30.3246756</v>
+        <v>24.131</v>
       </c>
       <c r="P51">
-        <v>121.2987024</v>
+        <v>96.524</v>
       </c>
       <c r="Q51">
-        <v>330.8987024</v>
+        <v>306.124</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.118950630667426</v>
+        <v>0.1202482028300411</v>
       </c>
       <c r="T51">
-        <v>1.504053958895069</v>
+        <v>1.5307334082768</v>
       </c>
       <c r="U51">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V51">
         <v>0.2</v>
       </c>
       <c r="W51">
-        <v>0.06064000000000001</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y51">
-        <v>2.035844221080604</v>
+        <v>1.68034057909724</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09612410141502054</v>
+        <v>0.09630338118965383</v>
       </c>
       <c r="C52">
-        <v>1528.910212925408</v>
+        <v>1483.209932251618</v>
       </c>
       <c r="D52">
-        <v>3015.810212925408</v>
+        <v>3009.519932251618</v>
       </c>
       <c r="E52">
-        <v>1141.4</v>
+        <v>1180.81</v>
       </c>
       <c r="F52">
-        <v>1970.5</v>
+        <v>2009.91</v>
       </c>
       <c r="G52">
         <v>483.6</v>
@@ -5557,28 +5557,28 @@
         <v>298</v>
       </c>
       <c r="M52">
-        <v>177.345</v>
+        <v>180.8919</v>
       </c>
       <c r="N52">
-        <v>120.655</v>
+        <v>117.1081</v>
       </c>
       <c r="O52">
-        <v>24.131</v>
+        <v>23.42162</v>
       </c>
       <c r="P52">
-        <v>96.524</v>
+        <v>93.68648</v>
       </c>
       <c r="Q52">
-        <v>306.124</v>
+        <v>303.28648</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1202482028300411</v>
+        <v>0.1215987371217425</v>
       </c>
       <c r="T52">
-        <v>1.5307334082768</v>
+        <v>1.558501814776152</v>
       </c>
       <c r="U52">
         <v>0.09</v>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>1.68034057909724</v>
+        <v>1.647392724605137</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.09630338118965383</v>
+        <v>0.09648266096428712</v>
       </c>
       <c r="C53">
-        <v>1483.209932251618</v>
+        <v>1437.535837094186</v>
       </c>
       <c r="D53">
-        <v>3009.519932251618</v>
+        <v>3003.255837094186</v>
       </c>
       <c r="E53">
-        <v>1180.81</v>
+        <v>1220.22</v>
       </c>
       <c r="F53">
-        <v>2009.91</v>
+        <v>2049.32</v>
       </c>
       <c r="G53">
         <v>483.6</v>
@@ -5639,28 +5639,28 @@
         <v>298</v>
       </c>
       <c r="M53">
-        <v>180.8919</v>
+        <v>184.4388</v>
       </c>
       <c r="N53">
-        <v>117.1081</v>
+        <v>113.5612</v>
       </c>
       <c r="O53">
-        <v>23.42162</v>
+        <v>22.71224</v>
       </c>
       <c r="P53">
-        <v>93.68648</v>
+        <v>90.84895999999999</v>
       </c>
       <c r="Q53">
-        <v>303.28648</v>
+        <v>300.44896</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1215987371217425</v>
+        <v>0.1230055436755982</v>
       </c>
       <c r="T53">
-        <v>1.558501814776152</v>
+        <v>1.587427238212977</v>
       </c>
       <c r="U53">
         <v>0.09</v>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>1.647392724605137</v>
+        <v>1.615712095285808</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.09648266096428712</v>
+        <v>0.09666194073892041</v>
       </c>
       <c r="C54">
-        <v>1437.535837094186</v>
+        <v>1391.887764283039</v>
       </c>
       <c r="D54">
-        <v>3003.255837094186</v>
+        <v>2997.017764283039</v>
       </c>
       <c r="E54">
-        <v>1220.22</v>
+        <v>1259.63</v>
       </c>
       <c r="F54">
-        <v>2049.32</v>
+        <v>2088.73</v>
       </c>
       <c r="G54">
         <v>483.6</v>
@@ -5721,28 +5721,28 @@
         <v>298</v>
       </c>
       <c r="M54">
-        <v>184.4388</v>
+        <v>187.9857</v>
       </c>
       <c r="N54">
-        <v>113.5612</v>
+        <v>110.0143</v>
       </c>
       <c r="O54">
-        <v>22.71224</v>
+        <v>22.00286</v>
       </c>
       <c r="P54">
-        <v>90.84895999999999</v>
+        <v>88.01143999999999</v>
       </c>
       <c r="Q54">
-        <v>300.44896</v>
+        <v>297.61144</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1230055436755982</v>
+        <v>0.1244722143381286</v>
       </c>
       <c r="T54">
-        <v>1.587427238212977</v>
+        <v>1.617583530732221</v>
       </c>
       <c r="U54">
         <v>0.09</v>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>1.615712095285808</v>
+        <v>1.58522696141249</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.09666194073892041</v>
+        <v>0.09684122051355371</v>
       </c>
       <c r="C55">
-        <v>1391.887764283039</v>
+        <v>1346.265552000979</v>
       </c>
       <c r="D55">
-        <v>2997.017764283039</v>
+        <v>2990.805552000979</v>
       </c>
       <c r="E55">
-        <v>1259.63</v>
+        <v>1299.04</v>
       </c>
       <c r="F55">
-        <v>2088.73</v>
+        <v>2128.14</v>
       </c>
       <c r="G55">
         <v>483.6</v>
@@ -5803,28 +5803,28 @@
         <v>298</v>
       </c>
       <c r="M55">
-        <v>187.9857</v>
+        <v>191.5326</v>
       </c>
       <c r="N55">
-        <v>110.0143</v>
+        <v>106.4674</v>
       </c>
       <c r="O55">
-        <v>22.00286</v>
+        <v>21.29348</v>
       </c>
       <c r="P55">
-        <v>88.01143999999999</v>
+        <v>85.17391999999998</v>
       </c>
       <c r="Q55">
-        <v>297.61144</v>
+        <v>294.77392</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1244722143381286</v>
+        <v>0.1260026532903341</v>
       </c>
       <c r="T55">
-        <v>1.617583530732221</v>
+        <v>1.649050966404475</v>
       </c>
       <c r="U55">
         <v>0.09</v>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>1.58522696141249</v>
+        <v>1.555870906571518</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.09684122051355371</v>
+        <v>0.09702050028818698</v>
       </c>
       <c r="C56">
-        <v>1346.265552000979</v>
+        <v>1300.66903976969</v>
       </c>
       <c r="D56">
-        <v>2990.805552000979</v>
+        <v>2984.619039769691</v>
       </c>
       <c r="E56">
-        <v>1299.04</v>
+        <v>1338.45</v>
       </c>
       <c r="F56">
-        <v>2128.14</v>
+        <v>2167.55</v>
       </c>
       <c r="G56">
         <v>483.6</v>
@@ -5885,28 +5885,28 @@
         <v>298</v>
       </c>
       <c r="M56">
-        <v>191.5326</v>
+        <v>195.0795</v>
       </c>
       <c r="N56">
-        <v>106.4674</v>
+        <v>102.9205</v>
       </c>
       <c r="O56">
-        <v>21.29348</v>
+        <v>20.5841</v>
       </c>
       <c r="P56">
-        <v>85.17391999999998</v>
+        <v>82.3364</v>
       </c>
       <c r="Q56">
-        <v>294.77392</v>
+        <v>291.9364</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1260026532903341</v>
+        <v>0.1276011117515266</v>
       </c>
       <c r="T56">
-        <v>1.649050966404475</v>
+        <v>1.681916954773274</v>
       </c>
       <c r="U56">
         <v>0.09</v>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>1.555870906571518</v>
+        <v>1.527582344633855</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.09702050028818698</v>
+        <v>0.09719978006282029</v>
       </c>
       <c r="C57">
-        <v>1300.66903976969</v>
+        <v>1255.09806843592</v>
       </c>
       <c r="D57">
-        <v>2984.619039769691</v>
+        <v>2978.45806843592</v>
       </c>
       <c r="E57">
-        <v>1338.45</v>
+        <v>1377.86</v>
       </c>
       <c r="F57">
-        <v>2167.55</v>
+        <v>2206.96</v>
       </c>
       <c r="G57">
         <v>483.6</v>
@@ -5967,28 +5967,28 @@
         <v>298</v>
       </c>
       <c r="M57">
-        <v>195.0795</v>
+        <v>198.6264</v>
       </c>
       <c r="N57">
-        <v>102.9205</v>
+        <v>99.37360000000001</v>
       </c>
       <c r="O57">
-        <v>20.5841</v>
+        <v>19.87472</v>
       </c>
       <c r="P57">
-        <v>82.3364</v>
+        <v>79.49888000000001</v>
       </c>
       <c r="Q57">
-        <v>291.9364</v>
+        <v>289.09888</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1276011117515266</v>
+        <v>0.1292722274155007</v>
       </c>
       <c r="T57">
-        <v>1.681916954773274</v>
+        <v>1.716276851704291</v>
       </c>
       <c r="U57">
         <v>0.09</v>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>1.527582344633855</v>
+        <v>1.500304088479679</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.09719978006282029</v>
+        <v>0.1253462049559436</v>
       </c>
       <c r="C58">
-        <v>1255.09806843592</v>
+        <v>486.6847742964155</v>
       </c>
       <c r="D58">
-        <v>2978.45806843592</v>
+        <v>2249.454774296416</v>
       </c>
       <c r="E58">
-        <v>1377.86</v>
+        <v>1417.27</v>
       </c>
       <c r="F58">
-        <v>2206.96</v>
+        <v>2246.37</v>
       </c>
       <c r="G58">
         <v>483.6</v>
@@ -6049,45 +6049,45 @@
         <v>298</v>
       </c>
       <c r="M58">
-        <v>198.6264</v>
+        <v>329.7671160000001</v>
       </c>
       <c r="N58">
-        <v>99.37360000000001</v>
+        <v>-31.7671160000001</v>
       </c>
       <c r="O58">
-        <v>19.87472</v>
+        <v>-6.35342320000002</v>
       </c>
       <c r="P58">
-        <v>79.49888000000001</v>
+        <v>-25.41369280000008</v>
       </c>
       <c r="Q58">
-        <v>289.09888</v>
+        <v>184.1863071999999</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1292722274155007</v>
+        <v>0.1320773724832993</v>
       </c>
       <c r="T58">
-        <v>1.716276851704291</v>
+        <v>1.773953586764571</v>
       </c>
       <c r="U58">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V58">
-        <v>0.2</v>
+        <v>0.1807336059548157</v>
       </c>
       <c r="W58">
-        <v>0.07199999999999999</v>
+        <v>0.1202683066458331</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y58">
-        <v>1.500304088479679</v>
+        <v>0.9036680297740782</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1253462049559436</v>
+        <v>0.1263562049559436</v>
       </c>
       <c r="C59">
-        <v>486.6847742964155</v>
+        <v>427.6901292554317</v>
       </c>
       <c r="D59">
-        <v>2249.454774296416</v>
+        <v>2229.870129255432</v>
       </c>
       <c r="E59">
-        <v>1417.27</v>
+        <v>1456.68</v>
       </c>
       <c r="F59">
-        <v>2246.37</v>
+        <v>2285.78</v>
       </c>
       <c r="G59">
         <v>483.6</v>
@@ -6131,37 +6131,37 @@
         <v>298</v>
       </c>
       <c r="M59">
-        <v>329.7671160000001</v>
+        <v>335.5525040000001</v>
       </c>
       <c r="N59">
-        <v>-31.7671160000001</v>
+        <v>-37.55250400000006</v>
       </c>
       <c r="O59">
-        <v>-6.35342320000002</v>
+        <v>-7.510500800000012</v>
       </c>
       <c r="P59">
-        <v>-25.41369280000008</v>
+        <v>-30.04200320000005</v>
       </c>
       <c r="Q59">
-        <v>184.1863071999999</v>
+        <v>179.5579968</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1320773724832993</v>
+        <v>0.1341315956376636</v>
       </c>
       <c r="T59">
-        <v>1.773953586764571</v>
+        <v>1.816190576925633</v>
       </c>
       <c r="U59">
         <v>0.1468</v>
       </c>
       <c r="V59">
-        <v>0.1807336059548157</v>
+        <v>0.1776175093004223</v>
       </c>
       <c r="W59">
-        <v>0.1202683066458331</v>
+        <v>0.120725749634698</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.9036680297740782</v>
+        <v>0.8880875465021115</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1263562049559435</v>
+        <v>0.1273662049559435</v>
       </c>
       <c r="C60">
-        <v>427.690129255433</v>
+        <v>369.0335641244869</v>
       </c>
       <c r="D60">
-        <v>2229.870129255433</v>
+        <v>2210.623564124487</v>
       </c>
       <c r="E60">
-        <v>1456.68</v>
+        <v>1496.09</v>
       </c>
       <c r="F60">
-        <v>2285.78</v>
+        <v>2325.19</v>
       </c>
       <c r="G60">
         <v>483.6</v>
@@ -6213,37 +6213,37 @@
         <v>298</v>
       </c>
       <c r="M60">
-        <v>335.552504</v>
+        <v>341.3378920000001</v>
       </c>
       <c r="N60">
-        <v>-37.552504</v>
+        <v>-43.33789200000007</v>
       </c>
       <c r="O60">
-        <v>-7.5105008</v>
+        <v>-8.667578400000014</v>
       </c>
       <c r="P60">
-        <v>-30.0420032</v>
+        <v>-34.67031360000006</v>
       </c>
       <c r="Q60">
-        <v>179.5579968</v>
+        <v>174.9296863999999</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1341315956376636</v>
+        <v>0.1362860247995578</v>
       </c>
       <c r="T60">
-        <v>1.816190576925632</v>
+        <v>1.86048790807016</v>
       </c>
       <c r="U60">
         <v>0.1468</v>
       </c>
       <c r="V60">
-        <v>0.1776175093004223</v>
+        <v>0.1746070430410931</v>
       </c>
       <c r="W60">
-        <v>0.120725749634698</v>
+        <v>0.1211676860815675</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.8880875465021116</v>
+        <v>0.8730352152054655</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1273662049559435</v>
+        <v>0.1283762049559435</v>
       </c>
       <c r="C61">
-        <v>369.0335641244869</v>
+        <v>310.7063996602692</v>
       </c>
       <c r="D61">
-        <v>2210.623564124487</v>
+        <v>2191.706399660269</v>
       </c>
       <c r="E61">
-        <v>1496.09</v>
+        <v>1535.5</v>
       </c>
       <c r="F61">
-        <v>2325.19</v>
+        <v>2364.6</v>
       </c>
       <c r="G61">
         <v>483.6</v>
@@ -6295,37 +6295,37 @@
         <v>298</v>
       </c>
       <c r="M61">
-        <v>341.3378920000001</v>
+        <v>347.12328</v>
       </c>
       <c r="N61">
-        <v>-43.33789200000007</v>
+        <v>-49.12328000000002</v>
       </c>
       <c r="O61">
-        <v>-8.667578400000014</v>
+        <v>-9.824656000000004</v>
       </c>
       <c r="P61">
-        <v>-34.67031360000006</v>
+        <v>-39.29862400000002</v>
       </c>
       <c r="Q61">
-        <v>174.9296863999999</v>
+        <v>170.301376</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1362860247995578</v>
+        <v>0.1385481754195467</v>
       </c>
       <c r="T61">
-        <v>1.86048790807016</v>
+        <v>1.907000105771913</v>
       </c>
       <c r="U61">
         <v>0.1468</v>
       </c>
       <c r="V61">
-        <v>0.1746070430410931</v>
+        <v>0.1716969256570749</v>
       </c>
       <c r="W61">
-        <v>0.1211676860815675</v>
+        <v>0.1215948913135414</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.8730352152054655</v>
+        <v>0.8584846282853745</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1283762049559435</v>
+        <v>0.1293862049559436</v>
       </c>
       <c r="C62">
-        <v>310.7063996602692</v>
+        <v>252.7002511853784</v>
       </c>
       <c r="D62">
-        <v>2191.706399660269</v>
+        <v>2173.110251185378</v>
       </c>
       <c r="E62">
-        <v>1535.5</v>
+        <v>1574.91</v>
       </c>
       <c r="F62">
-        <v>2364.6</v>
+        <v>2404.01</v>
       </c>
       <c r="G62">
         <v>483.6</v>
@@ -6377,37 +6377,37 @@
         <v>298</v>
       </c>
       <c r="M62">
-        <v>347.12328</v>
+        <v>352.908668</v>
       </c>
       <c r="N62">
-        <v>-49.12328000000002</v>
+        <v>-54.90866799999998</v>
       </c>
       <c r="O62">
-        <v>-9.824656000000004</v>
+        <v>-10.9817336</v>
       </c>
       <c r="P62">
-        <v>-39.29862400000002</v>
+        <v>-43.92693439999998</v>
       </c>
       <c r="Q62">
-        <v>170.301376</v>
+        <v>165.6730656</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1385481754195467</v>
+        <v>0.1409263337636377</v>
       </c>
       <c r="T62">
-        <v>1.907000105771913</v>
+        <v>1.95589754438145</v>
       </c>
       <c r="U62">
         <v>0.1468</v>
       </c>
       <c r="V62">
-        <v>0.1716969256570749</v>
+        <v>0.1688822219577786</v>
       </c>
       <c r="W62">
-        <v>0.1215948913135414</v>
+        <v>0.1220080898165981</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.8584846282853745</v>
+        <v>0.8444111097888931</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1293862049559436</v>
+        <v>0.1303962049559436</v>
       </c>
       <c r="C63">
-        <v>252.7002511853784</v>
+        <v>195.0070161968256</v>
       </c>
       <c r="D63">
-        <v>2173.110251185378</v>
+        <v>2154.827016196826</v>
       </c>
       <c r="E63">
-        <v>1574.91</v>
+        <v>1614.32</v>
       </c>
       <c r="F63">
-        <v>2404.01</v>
+        <v>2443.42</v>
       </c>
       <c r="G63">
         <v>483.6</v>
@@ -6459,37 +6459,37 @@
         <v>298</v>
       </c>
       <c r="M63">
-        <v>352.908668</v>
+        <v>358.694056</v>
       </c>
       <c r="N63">
-        <v>-54.90866799999998</v>
+        <v>-60.69405600000005</v>
       </c>
       <c r="O63">
-        <v>-10.9817336</v>
+        <v>-12.13881120000001</v>
       </c>
       <c r="P63">
-        <v>-43.92693439999998</v>
+        <v>-48.55524480000004</v>
       </c>
       <c r="Q63">
-        <v>165.6730656</v>
+        <v>161.0447551999999</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1409263337636377</v>
+        <v>0.143429658336365</v>
       </c>
       <c r="T63">
-        <v>1.95589754438145</v>
+        <v>2.007368532391488</v>
       </c>
       <c r="U63">
         <v>0.1468</v>
       </c>
       <c r="V63">
-        <v>0.1688822219577786</v>
+        <v>0.166158315152008</v>
       </c>
       <c r="W63">
-        <v>0.1220080898165981</v>
+        <v>0.1224079593356852</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.8444111097888931</v>
+        <v>0.8307915757600398</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1303962049559436</v>
+        <v>0.1314062049559435</v>
       </c>
       <c r="C64">
-        <v>195.0070161968256</v>
+        <v>137.6188625948485</v>
       </c>
       <c r="D64">
-        <v>2154.827016196826</v>
+        <v>2136.848862594848</v>
       </c>
       <c r="E64">
-        <v>1614.32</v>
+        <v>1653.73</v>
       </c>
       <c r="F64">
-        <v>2443.42</v>
+        <v>2482.83</v>
       </c>
       <c r="G64">
         <v>483.6</v>
@@ -6541,37 +6541,37 @@
         <v>298</v>
       </c>
       <c r="M64">
-        <v>358.694056</v>
+        <v>364.479444</v>
       </c>
       <c r="N64">
-        <v>-60.69405600000005</v>
+        <v>-66.479444</v>
       </c>
       <c r="O64">
-        <v>-12.13881120000001</v>
+        <v>-13.2958888</v>
       </c>
       <c r="P64">
-        <v>-48.55524480000004</v>
+        <v>-53.1835552</v>
       </c>
       <c r="Q64">
-        <v>161.0447551999999</v>
+        <v>156.4164448</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.143429658336365</v>
+        <v>0.1460682977508613</v>
       </c>
       <c r="T64">
-        <v>2.007368532391488</v>
+        <v>2.061621735969636</v>
       </c>
       <c r="U64">
         <v>0.1468</v>
       </c>
       <c r="V64">
-        <v>0.166158315152008</v>
+        <v>0.1635208815781666</v>
       </c>
       <c r="W64">
-        <v>0.1224079593356852</v>
+        <v>0.1227951345843252</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.8307915757600398</v>
+        <v>0.8176044078908329</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1314062049559435</v>
+        <v>0.1324162049559435</v>
       </c>
       <c r="C65">
-        <v>137.6188625948485</v>
+        <v>80.52821749609893</v>
       </c>
       <c r="D65">
-        <v>2136.848862594848</v>
+        <v>2119.168217496099</v>
       </c>
       <c r="E65">
-        <v>1653.73</v>
+        <v>1693.14</v>
       </c>
       <c r="F65">
-        <v>2482.83</v>
+        <v>2522.24</v>
       </c>
       <c r="G65">
         <v>483.6</v>
@@ -6623,37 +6623,37 @@
         <v>298</v>
       </c>
       <c r="M65">
-        <v>364.479444</v>
+        <v>370.2648320000001</v>
       </c>
       <c r="N65">
-        <v>-66.479444</v>
+        <v>-72.26483200000007</v>
       </c>
       <c r="O65">
-        <v>-13.2958888</v>
+        <v>-14.45296640000002</v>
       </c>
       <c r="P65">
-        <v>-53.1835552</v>
+        <v>-57.81186560000005</v>
       </c>
       <c r="Q65">
-        <v>156.4164448</v>
+        <v>151.7881343999999</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1460682977508613</v>
+        <v>0.1488535282439408</v>
       </c>
       <c r="T65">
-        <v>2.061621735969636</v>
+        <v>2.118889006413238</v>
       </c>
       <c r="U65">
         <v>0.1468</v>
       </c>
       <c r="V65">
-        <v>0.1635208815781666</v>
+        <v>0.1609658678035077</v>
       </c>
       <c r="W65">
-        <v>0.1227951345843252</v>
+        <v>0.1231702106064451</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.8176044078908329</v>
+        <v>0.8048293390175385</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1324162049559435</v>
+        <v>0.1696720490587275</v>
       </c>
       <c r="C66">
-        <v>80.52821749609893</v>
+        <v>-454.4263358314474</v>
       </c>
       <c r="D66">
-        <v>2119.168217496099</v>
+        <v>1623.623664168553</v>
       </c>
       <c r="E66">
-        <v>1693.14</v>
+        <v>1732.55</v>
       </c>
       <c r="F66">
-        <v>2522.24</v>
+        <v>2561.65</v>
       </c>
       <c r="G66">
         <v>483.6</v>
@@ -6705,45 +6705,45 @@
         <v>298</v>
       </c>
       <c r="M66">
-        <v>370.2648320000001</v>
+        <v>514.37932</v>
       </c>
       <c r="N66">
-        <v>-72.26483200000007</v>
+        <v>-216.37932</v>
       </c>
       <c r="O66">
-        <v>-14.45296640000002</v>
+        <v>-43.27586400000001</v>
       </c>
       <c r="P66">
-        <v>-57.81186560000005</v>
+        <v>-173.103456</v>
       </c>
       <c r="Q66">
-        <v>151.7881343999999</v>
+        <v>36.496544</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1488535282439408</v>
+        <v>0.1550717550588648</v>
       </c>
       <c r="T66">
-        <v>2.118889006413238</v>
+        <v>2.246742294525196</v>
       </c>
       <c r="U66">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.1609658678035077</v>
+        <v>0.1158677996619304</v>
       </c>
       <c r="W66">
-        <v>0.1231702106064451</v>
+        <v>0.1775337458278844</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y66">
-        <v>0.8048293390175385</v>
+        <v>0.5793389983096521</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1696720490587275</v>
+        <v>0.1712220490587275</v>
       </c>
       <c r="C67">
-        <v>-454.4263358314474</v>
+        <v>-509.4798831407643</v>
       </c>
       <c r="D67">
-        <v>1623.623664168553</v>
+        <v>1607.980116859236</v>
       </c>
       <c r="E67">
-        <v>1732.55</v>
+        <v>1771.96</v>
       </c>
       <c r="F67">
-        <v>2561.65</v>
+        <v>2601.06</v>
       </c>
       <c r="G67">
         <v>483.6</v>
@@ -6787,37 +6787,37 @@
         <v>298</v>
       </c>
       <c r="M67">
-        <v>514.37932</v>
+        <v>522.292848</v>
       </c>
       <c r="N67">
-        <v>-216.37932</v>
+        <v>-224.292848</v>
       </c>
       <c r="O67">
-        <v>-43.27586400000001</v>
+        <v>-44.85856960000001</v>
       </c>
       <c r="P67">
-        <v>-173.103456</v>
+        <v>-179.4342784</v>
       </c>
       <c r="Q67">
-        <v>36.496544</v>
+        <v>30.16572159999996</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1550717550588648</v>
+        <v>0.1582856302076549</v>
       </c>
       <c r="T67">
-        <v>2.246742294525196</v>
+        <v>2.312822950246525</v>
       </c>
       <c r="U67">
         <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.1158677996619304</v>
+        <v>0.11411222693978</v>
       </c>
       <c r="W67">
-        <v>0.1775337458278844</v>
+        <v>0.1778862648304922</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.5793389983096521</v>
+        <v>0.5705611346988997</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1712220490587275</v>
+        <v>0.1727720490587275</v>
       </c>
       <c r="C68">
-        <v>-509.4798831407643</v>
+        <v>-564.2348573184959</v>
       </c>
       <c r="D68">
-        <v>1607.980116859236</v>
+        <v>1592.635142681504</v>
       </c>
       <c r="E68">
-        <v>1771.96</v>
+        <v>1811.37</v>
       </c>
       <c r="F68">
-        <v>2601.06</v>
+        <v>2640.47</v>
       </c>
       <c r="G68">
         <v>483.6</v>
@@ -6869,37 +6869,37 @@
         <v>298</v>
       </c>
       <c r="M68">
-        <v>522.292848</v>
+        <v>530.2063760000001</v>
       </c>
       <c r="N68">
-        <v>-224.292848</v>
+        <v>-232.2063760000001</v>
       </c>
       <c r="O68">
-        <v>-44.85856960000001</v>
+        <v>-46.44127520000002</v>
       </c>
       <c r="P68">
-        <v>-179.4342784</v>
+        <v>-185.7651008000001</v>
       </c>
       <c r="Q68">
-        <v>30.16572159999996</v>
+        <v>23.83489919999991</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1582856302076549</v>
+        <v>0.161694285668493</v>
       </c>
       <c r="T68">
-        <v>2.312822950246525</v>
+        <v>2.38290849419339</v>
       </c>
       <c r="U68">
         <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.11411222693978</v>
+        <v>0.1124090593735146</v>
       </c>
       <c r="W68">
-        <v>0.1778862648304922</v>
+        <v>0.1782282608777983</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.5705611346988997</v>
+        <v>0.5620452968675729</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1727720490587275</v>
+        <v>0.1743220490587275</v>
       </c>
       <c r="C69">
-        <v>-564.2348573184959</v>
+        <v>-618.6997254246639</v>
       </c>
       <c r="D69">
-        <v>1592.635142681504</v>
+        <v>1577.580274575336</v>
       </c>
       <c r="E69">
-        <v>1811.37</v>
+        <v>1850.78</v>
       </c>
       <c r="F69">
-        <v>2640.47</v>
+        <v>2679.88</v>
       </c>
       <c r="G69">
         <v>483.6</v>
@@ -6951,37 +6951,37 @@
         <v>298</v>
       </c>
       <c r="M69">
-        <v>530.2063760000001</v>
+        <v>538.119904</v>
       </c>
       <c r="N69">
-        <v>-232.2063760000001</v>
+        <v>-240.119904</v>
       </c>
       <c r="O69">
-        <v>-46.44127520000002</v>
+        <v>-48.0239808</v>
       </c>
       <c r="P69">
-        <v>-185.7651008000001</v>
+        <v>-192.0959232</v>
       </c>
       <c r="Q69">
-        <v>23.83489919999991</v>
+        <v>17.50407679999998</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.161694285668493</v>
+        <v>0.1653159820956334</v>
       </c>
       <c r="T69">
-        <v>2.38290849419339</v>
+        <v>2.457374384636933</v>
       </c>
       <c r="U69">
         <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.1124090593735146</v>
+        <v>0.1107559849709629</v>
       </c>
       <c r="W69">
-        <v>0.1782282608777983</v>
+        <v>0.1785601982178306</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.5620452968675729</v>
+        <v>0.5537799248548145</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1743220490587275</v>
+        <v>0.1758720490587275</v>
       </c>
       <c r="C70">
-        <v>-618.6997254246639</v>
+        <v>-672.882637367426</v>
       </c>
       <c r="D70">
-        <v>1577.580274575336</v>
+        <v>1562.807362632574</v>
       </c>
       <c r="E70">
-        <v>1850.78</v>
+        <v>1890.190000000001</v>
       </c>
       <c r="F70">
-        <v>2679.88</v>
+        <v>2719.29</v>
       </c>
       <c r="G70">
         <v>483.6</v>
@@ -7033,37 +7033,37 @@
         <v>298</v>
       </c>
       <c r="M70">
-        <v>538.119904</v>
+        <v>546.0334320000001</v>
       </c>
       <c r="N70">
-        <v>-240.119904</v>
+        <v>-248.0334320000001</v>
       </c>
       <c r="O70">
-        <v>-48.0239808</v>
+        <v>-49.60668640000002</v>
       </c>
       <c r="P70">
-        <v>-192.0959232</v>
+        <v>-198.4267456000001</v>
       </c>
       <c r="Q70">
-        <v>17.50407679999998</v>
+        <v>11.17325439999993</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1653159820956334</v>
+        <v>0.1691713363567828</v>
       </c>
       <c r="T70">
-        <v>2.457374384636933</v>
+        <v>2.536644526076834</v>
       </c>
       <c r="U70">
         <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.1107559849709629</v>
+        <v>0.1091508257684852</v>
       </c>
       <c r="W70">
-        <v>0.1785601982178306</v>
+        <v>0.1788825141856882</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.5537799248548145</v>
+        <v>0.5457541288424259</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1758720490587275</v>
+        <v>0.1774220490587275</v>
       </c>
       <c r="C71">
-        <v>-672.882637367426</v>
+        <v>-726.7914406148097</v>
       </c>
       <c r="D71">
-        <v>1562.807362632574</v>
+        <v>1548.308559385191</v>
       </c>
       <c r="E71">
-        <v>1890.190000000001</v>
+        <v>1929.6</v>
       </c>
       <c r="F71">
-        <v>2719.29</v>
+        <v>2758.7</v>
       </c>
       <c r="G71">
         <v>483.6</v>
@@ -7115,37 +7115,37 @@
         <v>298</v>
       </c>
       <c r="M71">
-        <v>546.0334320000001</v>
+        <v>553.9469600000001</v>
       </c>
       <c r="N71">
-        <v>-248.0334320000001</v>
+        <v>-255.9469600000001</v>
       </c>
       <c r="O71">
-        <v>-49.60668640000002</v>
+        <v>-51.18939200000003</v>
       </c>
       <c r="P71">
-        <v>-198.4267456000001</v>
+        <v>-204.7575680000001</v>
       </c>
       <c r="Q71">
-        <v>11.17325439999993</v>
+        <v>4.842431999999917</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1691713363567828</v>
+        <v>0.1732837142353423</v>
       </c>
       <c r="T71">
-        <v>2.536644526076834</v>
+        <v>2.621199343612729</v>
       </c>
       <c r="U71">
         <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.1091508257684852</v>
+        <v>0.1075915282575068</v>
       </c>
       <c r="W71">
-        <v>0.1788825141856882</v>
+        <v>0.1791956211258926</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.5457541288424259</v>
+        <v>0.537957641287534</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1774220490587275</v>
+        <v>0.1789720490587276</v>
       </c>
       <c r="C72">
-        <v>-726.7914406148097</v>
+        <v>-780.4336940950611</v>
       </c>
       <c r="D72">
-        <v>1548.308559385191</v>
+        <v>1534.076305904939</v>
       </c>
       <c r="E72">
-        <v>1929.6</v>
+        <v>1969.01</v>
       </c>
       <c r="F72">
-        <v>2758.7</v>
+        <v>2798.11</v>
       </c>
       <c r="G72">
         <v>483.6</v>
@@ -7197,37 +7197,37 @@
         <v>298</v>
       </c>
       <c r="M72">
-        <v>553.9469600000001</v>
+        <v>561.860488</v>
       </c>
       <c r="N72">
-        <v>-255.9469600000001</v>
+        <v>-263.860488</v>
       </c>
       <c r="O72">
-        <v>-51.18939200000003</v>
+        <v>-52.77209760000001</v>
       </c>
       <c r="P72">
-        <v>-204.7575680000001</v>
+        <v>-211.0883904</v>
       </c>
       <c r="Q72">
-        <v>4.842431999999917</v>
+        <v>-1.488390400000043</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1732837142353423</v>
+        <v>0.1776797043813886</v>
       </c>
       <c r="T72">
-        <v>2.621199343612729</v>
+        <v>2.711585527875238</v>
       </c>
       <c r="U72">
         <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.1075915282575068</v>
+        <v>0.1060761546200771</v>
       </c>
       <c r="W72">
-        <v>0.1791956211258926</v>
+        <v>0.1794999081522885</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.537957641287534</v>
+        <v>0.5303807731003858</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1789720490587275</v>
+        <v>0.1805220490587275</v>
       </c>
       <c r="C73">
-        <v>-780.4336940950602</v>
+        <v>-833.816681337325</v>
       </c>
       <c r="D73">
-        <v>1534.076305904939</v>
+        <v>1520.103318662675</v>
       </c>
       <c r="E73">
-        <v>1969.01</v>
+        <v>2008.42</v>
       </c>
       <c r="F73">
-        <v>2798.11</v>
+        <v>2837.52</v>
       </c>
       <c r="G73">
         <v>483.6</v>
@@ -7279,37 +7279,37 @@
         <v>298</v>
       </c>
       <c r="M73">
-        <v>561.8604879999999</v>
+        <v>569.774016</v>
       </c>
       <c r="N73">
-        <v>-263.8604879999999</v>
+        <v>-271.774016</v>
       </c>
       <c r="O73">
-        <v>-52.77209759999999</v>
+        <v>-54.35480319999999</v>
       </c>
       <c r="P73">
-        <v>-211.0883903999999</v>
+        <v>-217.4192128</v>
       </c>
       <c r="Q73">
-        <v>-1.488390399999929</v>
+        <v>-7.819212799999974</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1776797043813886</v>
+        <v>0.182389693823581</v>
       </c>
       <c r="T73">
-        <v>2.711585527875236</v>
+        <v>2.808427868156494</v>
       </c>
       <c r="U73">
         <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.1060761546200772</v>
+        <v>0.1046028746947983</v>
       </c>
       <c r="W73">
-        <v>0.1794999081522885</v>
+        <v>0.1797957427612845</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.5303807731003858</v>
+        <v>0.5230143734739916</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1805220490587275</v>
+        <v>0.1820720490587275</v>
       </c>
       <c r="C74">
-        <v>-833.816681337325</v>
+        <v>-886.9474229006728</v>
       </c>
       <c r="D74">
-        <v>1520.103318662675</v>
+        <v>1506.382577099327</v>
       </c>
       <c r="E74">
-        <v>2008.42</v>
+        <v>2047.83</v>
       </c>
       <c r="F74">
-        <v>2837.52</v>
+        <v>2876.93</v>
       </c>
       <c r="G74">
         <v>483.6</v>
@@ -7361,37 +7361,37 @@
         <v>298</v>
       </c>
       <c r="M74">
-        <v>569.774016</v>
+        <v>577.687544</v>
       </c>
       <c r="N74">
-        <v>-271.774016</v>
+        <v>-279.687544</v>
       </c>
       <c r="O74">
-        <v>-54.35480319999999</v>
+        <v>-55.9375088</v>
       </c>
       <c r="P74">
-        <v>-217.4192128</v>
+        <v>-223.7500352</v>
       </c>
       <c r="Q74">
-        <v>-7.819212799999974</v>
+        <v>-14.15003520000002</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.182389693823581</v>
+        <v>0.1874485713726025</v>
       </c>
       <c r="T74">
-        <v>2.808427868156494</v>
+        <v>2.912443715125253</v>
       </c>
       <c r="U74">
         <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.1046028746947983</v>
+        <v>0.1031699586030887</v>
       </c>
       <c r="W74">
-        <v>0.1797957427612845</v>
+        <v>0.1800834723124998</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.5230143734739916</v>
+        <v>0.5158497930154436</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1820720490587275</v>
+        <v>0.1836220490587275</v>
       </c>
       <c r="C75">
-        <v>-886.9474229006728</v>
+        <v>-939.8326881360258</v>
       </c>
       <c r="D75">
-        <v>1506.382577099327</v>
+        <v>1492.907311863974</v>
       </c>
       <c r="E75">
-        <v>2047.83</v>
+        <v>2087.24</v>
       </c>
       <c r="F75">
-        <v>2876.93</v>
+        <v>2916.34</v>
       </c>
       <c r="G75">
         <v>483.6</v>
@@ -7443,37 +7443,37 @@
         <v>298</v>
       </c>
       <c r="M75">
-        <v>577.687544</v>
+        <v>585.601072</v>
       </c>
       <c r="N75">
-        <v>-279.687544</v>
+        <v>-287.601072</v>
       </c>
       <c r="O75">
-        <v>-55.9375088</v>
+        <v>-57.52021440000001</v>
       </c>
       <c r="P75">
-        <v>-223.7500352</v>
+        <v>-230.0808576</v>
       </c>
       <c r="Q75">
-        <v>-14.15003520000002</v>
+        <v>-20.48085760000004</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1874485713726025</v>
+        <v>0.1928965933484718</v>
       </c>
       <c r="T75">
-        <v>2.912443715125253</v>
+        <v>3.02446078109161</v>
       </c>
       <c r="U75">
         <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.1031699586030887</v>
+        <v>0.1017757699733173</v>
       </c>
       <c r="W75">
-        <v>0.1800834723124998</v>
+        <v>0.1803634253893579</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.5158497930154436</v>
+        <v>0.5088788498665863</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1836220490587275</v>
+        <v>0.1851720490587275</v>
       </c>
       <c r="C76">
-        <v>-939.8326881360258</v>
+        <v>-992.4790063223777</v>
       </c>
       <c r="D76">
-        <v>1492.907311863974</v>
+        <v>1479.670993677622</v>
       </c>
       <c r="E76">
-        <v>2087.24</v>
+        <v>2126.65</v>
       </c>
       <c r="F76">
-        <v>2916.34</v>
+        <v>2955.75</v>
       </c>
       <c r="G76">
         <v>483.6</v>
@@ -7525,37 +7525,37 @@
         <v>298</v>
       </c>
       <c r="M76">
-        <v>585.601072</v>
+        <v>593.5146</v>
       </c>
       <c r="N76">
-        <v>-287.601072</v>
+        <v>-295.5146</v>
       </c>
       <c r="O76">
-        <v>-57.52021440000001</v>
+        <v>-59.10292</v>
       </c>
       <c r="P76">
-        <v>-230.0808576</v>
+        <v>-236.41168</v>
       </c>
       <c r="Q76">
-        <v>-20.48085760000004</v>
+        <v>-26.81168</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1928965933484718</v>
+        <v>0.1987804570824107</v>
       </c>
       <c r="T76">
-        <v>3.02446078109161</v>
+        <v>3.145439212335274</v>
       </c>
       <c r="U76">
         <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.1017757699733173</v>
+        <v>0.1004187597070064</v>
       </c>
       <c r="W76">
-        <v>0.1803634253893579</v>
+        <v>0.1806359130508331</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.5088788498665863</v>
+        <v>0.5020937985350318</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1851720490587275</v>
+        <v>0.2137844109944628</v>
       </c>
       <c r="C77">
-        <v>-992.4790063223777</v>
+        <v>-1239.999258837352</v>
       </c>
       <c r="D77">
-        <v>1479.670993677622</v>
+        <v>1271.560741162648</v>
       </c>
       <c r="E77">
-        <v>2126.65</v>
+        <v>2166.06</v>
       </c>
       <c r="F77">
-        <v>2955.75</v>
+        <v>2995.16</v>
       </c>
       <c r="G77">
         <v>483.6</v>
@@ -7607,45 +7607,45 @@
         <v>298</v>
       </c>
       <c r="M77">
-        <v>593.5146</v>
+        <v>706.258728</v>
       </c>
       <c r="N77">
-        <v>-295.5146</v>
+        <v>-408.258728</v>
       </c>
       <c r="O77">
-        <v>-59.10292</v>
+        <v>-81.65174560000001</v>
       </c>
       <c r="P77">
-        <v>-236.41168</v>
+        <v>-326.6069824</v>
       </c>
       <c r="Q77">
-        <v>-26.81168</v>
+        <v>-117.0069824</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1987804570824107</v>
+        <v>0.2070811508597414</v>
       </c>
       <c r="T77">
-        <v>3.145439212335274</v>
+        <v>3.316110213028769</v>
       </c>
       <c r="U77">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.1004187597070064</v>
+        <v>0.08438833764048011</v>
       </c>
       <c r="W77">
-        <v>0.1806359130508331</v>
+        <v>0.2159012299843748</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y77">
-        <v>0.5020937985350318</v>
+        <v>0.4219416882024005</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2137844109944628</v>
+        <v>0.2156844109944628</v>
       </c>
       <c r="C78">
-        <v>-1239.999258837352</v>
+        <v>-1291.175236124312</v>
       </c>
       <c r="D78">
-        <v>1271.560741162648</v>
+        <v>1259.794763875688</v>
       </c>
       <c r="E78">
-        <v>2166.06</v>
+        <v>2205.47</v>
       </c>
       <c r="F78">
-        <v>2995.16</v>
+        <v>3034.57</v>
       </c>
       <c r="G78">
         <v>483.6</v>
@@ -7689,37 +7689,37 @@
         <v>298</v>
       </c>
       <c r="M78">
-        <v>706.258728</v>
+        <v>715.5516060000001</v>
       </c>
       <c r="N78">
-        <v>-408.258728</v>
+        <v>-417.5516060000001</v>
       </c>
       <c r="O78">
-        <v>-81.65174560000001</v>
+        <v>-83.51032120000002</v>
       </c>
       <c r="P78">
-        <v>-326.6069824</v>
+        <v>-334.0412848000001</v>
       </c>
       <c r="Q78">
-        <v>-117.0069824</v>
+        <v>-124.4412848000001</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2070811508597414</v>
+        <v>0.2140933748101649</v>
       </c>
       <c r="T78">
-        <v>3.316110213028769</v>
+        <v>3.460288917943064</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.08438833764048011</v>
+        <v>0.08329238520359074</v>
       </c>
       <c r="W78">
-        <v>0.2159012299843748</v>
+        <v>0.2161596555689933</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.4219416882024005</v>
+        <v>0.4164619260179537</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2156844109944628</v>
+        <v>0.2175844109944628</v>
       </c>
       <c r="C79">
-        <v>-1291.175236124312</v>
+        <v>-1342.135464421514</v>
       </c>
       <c r="D79">
-        <v>1259.794763875688</v>
+        <v>1248.244535578486</v>
       </c>
       <c r="E79">
-        <v>2205.47</v>
+        <v>2244.88</v>
       </c>
       <c r="F79">
-        <v>3034.57</v>
+        <v>3073.98</v>
       </c>
       <c r="G79">
         <v>483.6</v>
@@ -7771,37 +7771,37 @@
         <v>298</v>
       </c>
       <c r="M79">
-        <v>715.5516060000001</v>
+        <v>724.8444840000001</v>
       </c>
       <c r="N79">
-        <v>-417.5516060000001</v>
+        <v>-426.8444840000001</v>
       </c>
       <c r="O79">
-        <v>-83.51032120000002</v>
+        <v>-85.36889680000002</v>
       </c>
       <c r="P79">
-        <v>-334.0412848000001</v>
+        <v>-341.4755872000001</v>
       </c>
       <c r="Q79">
-        <v>-124.4412848000001</v>
+        <v>-131.8755872000001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2140933748101649</v>
+        <v>0.2217430736651725</v>
       </c>
       <c r="T79">
-        <v>3.460288917943064</v>
+        <v>3.617574777849567</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.08329238520359074</v>
+        <v>0.08222453411123702</v>
       </c>
       <c r="W79">
-        <v>0.2161596555689933</v>
+        <v>0.2164114548565703</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.4164619260179537</v>
+        <v>0.4111226705561851</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2175844109944628</v>
+        <v>0.2194844109944628</v>
       </c>
       <c r="C80">
-        <v>-1342.135464421514</v>
+        <v>-1392.885823997733</v>
       </c>
       <c r="D80">
-        <v>1248.244535578486</v>
+        <v>1236.904176002267</v>
       </c>
       <c r="E80">
-        <v>2244.88</v>
+        <v>2284.29</v>
       </c>
       <c r="F80">
-        <v>3073.98</v>
+        <v>3113.39</v>
       </c>
       <c r="G80">
         <v>483.6</v>
@@ -7853,37 +7853,37 @@
         <v>298</v>
       </c>
       <c r="M80">
-        <v>724.8444840000001</v>
+        <v>734.1373620000001</v>
       </c>
       <c r="N80">
-        <v>-426.8444840000001</v>
+        <v>-436.1373620000001</v>
       </c>
       <c r="O80">
-        <v>-85.36889680000002</v>
+        <v>-87.22747240000001</v>
       </c>
       <c r="P80">
-        <v>-341.4755872000001</v>
+        <v>-348.9098896</v>
       </c>
       <c r="Q80">
-        <v>-131.8755872000001</v>
+        <v>-139.3098896</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2217430736651725</v>
+        <v>0.2301213152682759</v>
       </c>
       <c r="T80">
-        <v>3.617574777849567</v>
+        <v>3.789840243461451</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.08222453411123702</v>
+        <v>0.081183717223753</v>
       </c>
       <c r="W80">
-        <v>0.2164114548565703</v>
+        <v>0.216656879478639</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.4111226705561851</v>
+        <v>0.4059185861187651</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2194844109944628</v>
+        <v>0.2213844109944628</v>
       </c>
       <c r="C81">
-        <v>-1392.885823997733</v>
+        <v>-1443.431983355591</v>
       </c>
       <c r="D81">
-        <v>1236.904176002267</v>
+        <v>1225.768016644409</v>
       </c>
       <c r="E81">
-        <v>2284.29</v>
+        <v>2323.7</v>
       </c>
       <c r="F81">
-        <v>3113.39</v>
+        <v>3152.8</v>
       </c>
       <c r="G81">
         <v>483.6</v>
@@ -7935,37 +7935,37 @@
         <v>298</v>
       </c>
       <c r="M81">
-        <v>734.1373620000001</v>
+        <v>743.43024</v>
       </c>
       <c r="N81">
-        <v>-436.1373620000001</v>
+        <v>-445.43024</v>
       </c>
       <c r="O81">
-        <v>-87.22747240000001</v>
+        <v>-89.08604800000001</v>
       </c>
       <c r="P81">
-        <v>-348.9098896</v>
+        <v>-356.344192</v>
       </c>
       <c r="Q81">
-        <v>-139.3098896</v>
+        <v>-146.744192</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2301213152682759</v>
+        <v>0.2393373810316897</v>
       </c>
       <c r="T81">
-        <v>3.789840243461451</v>
+        <v>3.979332255634523</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.081183717223753</v>
+        <v>0.08016892075845611</v>
       </c>
       <c r="W81">
-        <v>0.216656879478639</v>
+        <v>0.2168961684851561</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.4059185861187651</v>
+        <v>0.4008446037922805</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2213844109944628</v>
+        <v>0.2232844109944628</v>
       </c>
       <c r="C82">
-        <v>-1443.431983355591</v>
+        <v>-1493.779408679412</v>
       </c>
       <c r="D82">
-        <v>1225.768016644409</v>
+        <v>1214.830591320588</v>
       </c>
       <c r="E82">
-        <v>2323.7</v>
+        <v>2363.11</v>
       </c>
       <c r="F82">
-        <v>3152.8</v>
+        <v>3192.21</v>
       </c>
       <c r="G82">
         <v>483.6</v>
@@ -8017,37 +8017,37 @@
         <v>298</v>
       </c>
       <c r="M82">
-        <v>743.43024</v>
+        <v>752.723118</v>
       </c>
       <c r="N82">
-        <v>-445.43024</v>
+        <v>-454.723118</v>
       </c>
       <c r="O82">
-        <v>-89.08604800000001</v>
+        <v>-90.9446236</v>
       </c>
       <c r="P82">
-        <v>-356.344192</v>
+        <v>-363.7784944</v>
       </c>
       <c r="Q82">
-        <v>-146.744192</v>
+        <v>-154.1784944</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2393373810316897</v>
+        <v>0.249523558980726</v>
       </c>
       <c r="T82">
-        <v>3.979332255634523</v>
+        <v>4.188770795404761</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.08016892075845611</v>
+        <v>0.07917918099600603</v>
       </c>
       <c r="W82">
-        <v>0.2168961684851561</v>
+        <v>0.2171295491211418</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.4008446037922805</v>
+        <v>0.3958959049800301</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2232844109944628</v>
+        <v>0.2251844109944628</v>
       </c>
       <c r="C83">
-        <v>-1493.779408679412</v>
+        <v>-1543.933372781741</v>
       </c>
       <c r="D83">
-        <v>1214.830591320588</v>
+        <v>1204.08662721826</v>
       </c>
       <c r="E83">
-        <v>2363.11</v>
+        <v>2402.52</v>
       </c>
       <c r="F83">
-        <v>3192.21</v>
+        <v>3231.62</v>
       </c>
       <c r="G83">
         <v>483.6</v>
@@ -8099,37 +8099,37 @@
         <v>298</v>
       </c>
       <c r="M83">
-        <v>752.723118</v>
+        <v>762.0159960000001</v>
       </c>
       <c r="N83">
-        <v>-454.723118</v>
+        <v>-464.0159960000001</v>
       </c>
       <c r="O83">
-        <v>-90.9446236</v>
+        <v>-92.80319920000002</v>
       </c>
       <c r="P83">
-        <v>-363.7784944</v>
+        <v>-371.2127968000001</v>
       </c>
       <c r="Q83">
-        <v>-154.1784944</v>
+        <v>-161.6127968000001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.249523558980726</v>
+        <v>0.2608415344796552</v>
       </c>
       <c r="T83">
-        <v>4.188770795404761</v>
+        <v>4.42148028403836</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.07917918099600603</v>
+        <v>0.07821358122776205</v>
       </c>
       <c r="W83">
-        <v>0.2171295491211418</v>
+        <v>0.2173572375464937</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3958959049800301</v>
+        <v>0.3910679061388102</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2251844109944628</v>
+        <v>0.2270844109944628</v>
       </c>
       <c r="C84">
-        <v>-1543.933372781741</v>
+        <v>-1593.898963579285</v>
       </c>
       <c r="D84">
-        <v>1204.08662721826</v>
+        <v>1193.531036420715</v>
       </c>
       <c r="E84">
-        <v>2402.52</v>
+        <v>2441.93</v>
       </c>
       <c r="F84">
-        <v>3231.62</v>
+        <v>3271.03</v>
       </c>
       <c r="G84">
         <v>483.6</v>
@@ -8181,37 +8181,37 @@
         <v>298</v>
       </c>
       <c r="M84">
-        <v>762.0159960000001</v>
+        <v>771.3088740000001</v>
       </c>
       <c r="N84">
-        <v>-464.0159960000001</v>
+        <v>-473.3088740000001</v>
       </c>
       <c r="O84">
-        <v>-92.80319920000002</v>
+        <v>-94.66177480000002</v>
       </c>
       <c r="P84">
-        <v>-371.2127968000001</v>
+        <v>-378.6470992000001</v>
       </c>
       <c r="Q84">
-        <v>-161.6127968000001</v>
+        <v>-169.0470992000001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2608415344796552</v>
+        <v>0.2734910365078703</v>
       </c>
       <c r="T84">
-        <v>4.42148028403836</v>
+        <v>4.681567359570029</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.07821358122776205</v>
+        <v>0.07727124892381311</v>
       </c>
       <c r="W84">
-        <v>0.2173572375464937</v>
+        <v>0.2175794395037649</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3910679061388102</v>
+        <v>0.3863562446190655</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2270844109944628</v>
+        <v>0.2289844109944628</v>
       </c>
       <c r="C85">
-        <v>-1593.898963579285</v>
+        <v>-1643.681092126907</v>
       </c>
       <c r="D85">
-        <v>1193.531036420715</v>
+        <v>1183.158907873094</v>
       </c>
       <c r="E85">
-        <v>2441.93</v>
+        <v>2481.340000000001</v>
       </c>
       <c r="F85">
-        <v>3271.03</v>
+        <v>3310.440000000001</v>
       </c>
       <c r="G85">
         <v>483.6</v>
@@ -8263,37 +8263,37 @@
         <v>298</v>
       </c>
       <c r="M85">
-        <v>771.3088740000001</v>
+        <v>780.6017520000001</v>
       </c>
       <c r="N85">
-        <v>-473.3088740000001</v>
+        <v>-482.6017520000001</v>
       </c>
       <c r="O85">
-        <v>-94.66177480000002</v>
+        <v>-96.52035040000004</v>
       </c>
       <c r="P85">
-        <v>-378.6470992000001</v>
+        <v>-386.0814016000001</v>
       </c>
       <c r="Q85">
-        <v>-169.0470992000001</v>
+        <v>-176.4814016000001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2734910365078703</v>
+        <v>0.2877217262896121</v>
       </c>
       <c r="T85">
-        <v>4.681567359570029</v>
+        <v>4.974165319543156</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.07727124892381311</v>
+        <v>0.07635135310329151</v>
       </c>
       <c r="W85">
-        <v>0.2175794395037649</v>
+        <v>0.2177963509382439</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3863562446190655</v>
+        <v>0.3817567655164575</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2289844109944628</v>
+        <v>0.2308844109944628</v>
       </c>
       <c r="C86">
-        <v>-1643.681092126906</v>
+        <v>-1693.284500236308</v>
       </c>
       <c r="D86">
-        <v>1183.158907873094</v>
+        <v>1172.965499763692</v>
       </c>
       <c r="E86">
-        <v>2481.34</v>
+        <v>2520.75</v>
       </c>
       <c r="F86">
-        <v>3310.44</v>
+        <v>3349.85</v>
       </c>
       <c r="G86">
         <v>483.6</v>
@@ -8345,37 +8345,37 @@
         <v>298</v>
       </c>
       <c r="M86">
-        <v>780.601752</v>
+        <v>789.89463</v>
       </c>
       <c r="N86">
-        <v>-482.601752</v>
+        <v>-491.89463</v>
       </c>
       <c r="O86">
-        <v>-96.52035040000001</v>
+        <v>-98.37892600000001</v>
       </c>
       <c r="P86">
-        <v>-386.0814016</v>
+        <v>-393.515704</v>
       </c>
       <c r="Q86">
-        <v>-176.4814016000001</v>
+        <v>-183.915704</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.287721726289612</v>
+        <v>0.3038498413755861</v>
       </c>
       <c r="T86">
-        <v>4.974165319543153</v>
+        <v>5.305776340846029</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.07635135310329152</v>
+        <v>0.07545310189031162</v>
       </c>
       <c r="W86">
-        <v>0.2177963509382439</v>
+        <v>0.2180081585742645</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3817567655164577</v>
+        <v>0.3772655094515581</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2308844109944628</v>
+        <v>0.2327844109944628</v>
       </c>
       <c r="C87">
-        <v>-1693.284500236308</v>
+        <v>-1742.713767704268</v>
       </c>
       <c r="D87">
-        <v>1172.965499763692</v>
+        <v>1162.946232295731</v>
       </c>
       <c r="E87">
-        <v>2520.75</v>
+        <v>2560.16</v>
       </c>
       <c r="F87">
-        <v>3349.85</v>
+        <v>3389.26</v>
       </c>
       <c r="G87">
         <v>483.6</v>
@@ -8427,37 +8427,37 @@
         <v>298</v>
       </c>
       <c r="M87">
-        <v>789.89463</v>
+        <v>799.187508</v>
       </c>
       <c r="N87">
-        <v>-491.89463</v>
+        <v>-501.187508</v>
       </c>
       <c r="O87">
-        <v>-98.37892600000001</v>
+        <v>-100.2375016</v>
       </c>
       <c r="P87">
-        <v>-393.515704</v>
+        <v>-400.9500064</v>
       </c>
       <c r="Q87">
-        <v>-183.915704</v>
+        <v>-191.3500064</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3038498413755861</v>
+        <v>0.3222819729024137</v>
       </c>
       <c r="T87">
-        <v>5.305776340846029</v>
+        <v>5.684760365192175</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.07545310189031162</v>
+        <v>0.07457574024042428</v>
       </c>
       <c r="W87">
-        <v>0.2180081585742645</v>
+        <v>0.218215040451308</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3772655094515581</v>
+        <v>0.3728787012021214</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2327844109944628</v>
+        <v>0.2346844109944628</v>
       </c>
       <c r="C88">
-        <v>-1742.713767704268</v>
+        <v>-1791.973319173554</v>
       </c>
       <c r="D88">
-        <v>1162.946232295731</v>
+        <v>1153.096680826447</v>
       </c>
       <c r="E88">
-        <v>2560.16</v>
+        <v>2599.57</v>
       </c>
       <c r="F88">
-        <v>3389.26</v>
+        <v>3428.67</v>
       </c>
       <c r="G88">
         <v>483.6</v>
@@ -8509,37 +8509,37 @@
         <v>298</v>
       </c>
       <c r="M88">
-        <v>799.187508</v>
+        <v>808.4803860000001</v>
       </c>
       <c r="N88">
-        <v>-501.187508</v>
+        <v>-510.4803860000001</v>
       </c>
       <c r="O88">
-        <v>-100.2375016</v>
+        <v>-102.0960772</v>
       </c>
       <c r="P88">
-        <v>-400.9500064</v>
+        <v>-408.3843088</v>
       </c>
       <c r="Q88">
-        <v>-191.3500064</v>
+        <v>-198.7843088</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3222819729024137</v>
+        <v>0.3435498169718302</v>
       </c>
       <c r="T88">
-        <v>5.684760365192175</v>
+        <v>6.122049624053112</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.07457574024042428</v>
+        <v>0.07371854782386768</v>
       </c>
       <c r="W88">
-        <v>0.218215040451308</v>
+        <v>0.218417166423132</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3728787012021214</v>
+        <v>0.3685927391193383</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2346844109944628</v>
+        <v>0.2365844109944628</v>
       </c>
       <c r="C89">
-        <v>-1791.973319173554</v>
+        <v>-1841.067430648103</v>
       </c>
       <c r="D89">
-        <v>1153.096680826447</v>
+        <v>1143.412569351897</v>
       </c>
       <c r="E89">
-        <v>2599.57</v>
+        <v>2638.98</v>
       </c>
       <c r="F89">
-        <v>3428.67</v>
+        <v>3468.08</v>
       </c>
       <c r="G89">
         <v>483.6</v>
@@ -8591,37 +8591,37 @@
         <v>298</v>
       </c>
       <c r="M89">
-        <v>808.4803860000001</v>
+        <v>817.773264</v>
       </c>
       <c r="N89">
-        <v>-510.4803860000001</v>
+        <v>-519.773264</v>
       </c>
       <c r="O89">
-        <v>-102.0960772</v>
+        <v>-103.9546528</v>
       </c>
       <c r="P89">
-        <v>-408.3843088</v>
+        <v>-415.8186112</v>
       </c>
       <c r="Q89">
-        <v>-198.7843088</v>
+        <v>-206.2186112</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3435498169718302</v>
+        <v>0.3683623017194828</v>
       </c>
       <c r="T89">
-        <v>6.122049624053112</v>
+        <v>6.632220426057539</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.07371854782386768</v>
+        <v>0.0728808370531419</v>
       </c>
       <c r="W89">
-        <v>0.218417166423132</v>
+        <v>0.2186146986228692</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3685927391193383</v>
+        <v>0.3644041852657095</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2365844109944628</v>
+        <v>0.2384844109944628</v>
       </c>
       <c r="C90">
-        <v>-1841.067430648103</v>
+        <v>-1890.000235682655</v>
       </c>
       <c r="D90">
-        <v>1143.412569351897</v>
+        <v>1133.889764317345</v>
       </c>
       <c r="E90">
-        <v>2638.98</v>
+        <v>2678.39</v>
       </c>
       <c r="F90">
-        <v>3468.08</v>
+        <v>3507.49</v>
       </c>
       <c r="G90">
         <v>483.6</v>
@@ -8673,37 +8673,37 @@
         <v>298</v>
       </c>
       <c r="M90">
-        <v>817.773264</v>
+        <v>827.0661420000001</v>
       </c>
       <c r="N90">
-        <v>-519.773264</v>
+        <v>-529.0661420000001</v>
       </c>
       <c r="O90">
-        <v>-103.9546528</v>
+        <v>-105.8132284</v>
       </c>
       <c r="P90">
-        <v>-415.8186112</v>
+        <v>-423.2529136000001</v>
       </c>
       <c r="Q90">
-        <v>-206.2186112</v>
+        <v>-213.6529136000001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3683623017194828</v>
+        <v>0.3976861473303448</v>
       </c>
       <c r="T90">
-        <v>6.632220426057539</v>
+        <v>7.235149555699133</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.0728808370531419</v>
+        <v>0.07206195124355604</v>
       </c>
       <c r="W90">
-        <v>0.2186146986228692</v>
+        <v>0.2188077918967695</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3644041852657095</v>
+        <v>0.3603097562177802</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2384844109944628</v>
+        <v>0.2403844109944628</v>
       </c>
       <c r="C91">
-        <v>-1890.000235682655</v>
+        <v>-1938.775731265628</v>
       </c>
       <c r="D91">
-        <v>1133.889764317345</v>
+        <v>1124.524268734373</v>
       </c>
       <c r="E91">
-        <v>2678.39</v>
+        <v>2717.8</v>
       </c>
       <c r="F91">
-        <v>3507.49</v>
+        <v>3546.9</v>
       </c>
       <c r="G91">
         <v>483.6</v>
@@ -8755,37 +8755,37 @@
         <v>298</v>
       </c>
       <c r="M91">
-        <v>827.0661420000001</v>
+        <v>836.3590200000001</v>
       </c>
       <c r="N91">
-        <v>-529.0661420000001</v>
+        <v>-538.3590200000001</v>
       </c>
       <c r="O91">
-        <v>-105.8132284</v>
+        <v>-107.671804</v>
       </c>
       <c r="P91">
-        <v>-423.2529136000001</v>
+        <v>-430.6872160000001</v>
       </c>
       <c r="Q91">
-        <v>-213.6529136000001</v>
+        <v>-221.0872160000001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3976861473303448</v>
+        <v>0.4328747620633793</v>
       </c>
       <c r="T91">
-        <v>7.235149555699133</v>
+        <v>7.958664511269046</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.07206195124355604</v>
+        <v>0.07126126289640541</v>
       </c>
       <c r="W91">
-        <v>0.2188077918967695</v>
+        <v>0.2189965942090276</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3603097562177802</v>
+        <v>0.3563063144820271</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2403844109944628</v>
+        <v>0.2422844109944628</v>
       </c>
       <c r="C92">
-        <v>-1938.775731265628</v>
+        <v>-1987.39778341284</v>
       </c>
       <c r="D92">
-        <v>1124.524268734373</v>
+        <v>1115.31221658716</v>
       </c>
       <c r="E92">
-        <v>2717.8</v>
+        <v>2757.21</v>
       </c>
       <c r="F92">
-        <v>3546.9</v>
+        <v>3586.31</v>
       </c>
       <c r="G92">
         <v>483.6</v>
@@ -8837,37 +8837,37 @@
         <v>298</v>
       </c>
       <c r="M92">
-        <v>836.3590200000001</v>
+        <v>845.6518980000001</v>
       </c>
       <c r="N92">
-        <v>-538.3590200000001</v>
+        <v>-547.6518980000001</v>
       </c>
       <c r="O92">
-        <v>-107.671804</v>
+        <v>-109.5303796</v>
       </c>
       <c r="P92">
-        <v>-430.6872160000001</v>
+        <v>-438.1215184000001</v>
       </c>
       <c r="Q92">
-        <v>-221.0872160000001</v>
+        <v>-228.5215184000001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4328747620633793</v>
+        <v>0.4758830689593104</v>
       </c>
       <c r="T92">
-        <v>7.958664511269046</v>
+        <v>8.84296056807672</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.07126126289640541</v>
+        <v>0.07047817209534601</v>
       </c>
       <c r="W92">
-        <v>0.2189965942090276</v>
+        <v>0.2191812470199174</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3563063144820271</v>
+        <v>0.3523908604767301</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2422844109944628</v>
+        <v>0.2441844109944628</v>
       </c>
       <c r="C93">
-        <v>-1987.39778341284</v>
+        <v>-2035.870132488536</v>
       </c>
       <c r="D93">
-        <v>1115.31221658716</v>
+        <v>1106.249867511465</v>
       </c>
       <c r="E93">
-        <v>2757.21</v>
+        <v>2796.62</v>
       </c>
       <c r="F93">
-        <v>3586.31</v>
+        <v>3625.72</v>
       </c>
       <c r="G93">
         <v>483.6</v>
@@ -8919,37 +8919,37 @@
         <v>298</v>
       </c>
       <c r="M93">
-        <v>845.6518980000001</v>
+        <v>854.944776</v>
       </c>
       <c r="N93">
-        <v>-547.6518980000001</v>
+        <v>-556.944776</v>
       </c>
       <c r="O93">
-        <v>-109.5303796</v>
+        <v>-111.3889552</v>
       </c>
       <c r="P93">
-        <v>-438.1215184000001</v>
+        <v>-445.5558208</v>
       </c>
       <c r="Q93">
-        <v>-228.5215184000001</v>
+        <v>-235.9558208000001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4758830689593104</v>
+        <v>0.5296434525792244</v>
       </c>
       <c r="T93">
-        <v>8.84296056807672</v>
+        <v>9.948330639086313</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.07047817209534601</v>
+        <v>0.06971210500735313</v>
       </c>
       <c r="W93">
-        <v>0.2191812470199174</v>
+        <v>0.2193618856392661</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3523908604767301</v>
+        <v>0.3485605250367656</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2441844109944628</v>
+        <v>0.2460844109944628</v>
       </c>
       <c r="C94">
-        <v>-2035.870132488536</v>
+        <v>-2084.196398269077</v>
       </c>
       <c r="D94">
-        <v>1106.249867511465</v>
+        <v>1097.333601730923</v>
       </c>
       <c r="E94">
-        <v>2796.62</v>
+        <v>2836.03</v>
       </c>
       <c r="F94">
-        <v>3625.72</v>
+        <v>3665.13</v>
       </c>
       <c r="G94">
         <v>483.6</v>
@@ -9001,37 +9001,37 @@
         <v>298</v>
       </c>
       <c r="M94">
-        <v>854.944776</v>
+        <v>864.237654</v>
       </c>
       <c r="N94">
-        <v>-556.944776</v>
+        <v>-566.237654</v>
       </c>
       <c r="O94">
-        <v>-111.3889552</v>
+        <v>-113.2475308</v>
       </c>
       <c r="P94">
-        <v>-445.5558208</v>
+        <v>-452.9901232</v>
       </c>
       <c r="Q94">
-        <v>-235.9558208000001</v>
+        <v>-243.3901232</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5296434525792244</v>
+        <v>0.5987639458048278</v>
       </c>
       <c r="T94">
-        <v>9.948330639086313</v>
+        <v>11.36952073038436</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.06971210500735313</v>
+        <v>0.06896251248039235</v>
       </c>
       <c r="W94">
-        <v>0.2193618856392661</v>
+        <v>0.2195386395571235</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3485605250367656</v>
+        <v>0.3448125624019617</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2460844109944628</v>
+        <v>0.2479844109944628</v>
       </c>
       <c r="C95">
-        <v>-2084.196398269077</v>
+        <v>-2132.380084763725</v>
       </c>
       <c r="D95">
-        <v>1097.333601730923</v>
+        <v>1088.559915236276</v>
       </c>
       <c r="E95">
-        <v>2836.03</v>
+        <v>2875.440000000001</v>
       </c>
       <c r="F95">
-        <v>3665.13</v>
+        <v>3704.54</v>
       </c>
       <c r="G95">
         <v>483.6</v>
@@ -9083,37 +9083,37 @@
         <v>298</v>
       </c>
       <c r="M95">
-        <v>864.237654</v>
+        <v>873.5305320000001</v>
       </c>
       <c r="N95">
-        <v>-566.237654</v>
+        <v>-575.5305320000001</v>
       </c>
       <c r="O95">
-        <v>-113.2475308</v>
+        <v>-115.1061064</v>
       </c>
       <c r="P95">
-        <v>-452.9901232</v>
+        <v>-460.4244256000001</v>
       </c>
       <c r="Q95">
-        <v>-243.3901232</v>
+        <v>-250.8244256000001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5987639458048278</v>
+        <v>0.690924603438966</v>
       </c>
       <c r="T95">
-        <v>11.36952073038436</v>
+        <v>13.26444085211509</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.06896251248039235</v>
+        <v>0.06822886873060093</v>
       </c>
       <c r="W95">
-        <v>0.2195386395571235</v>
+        <v>0.2197116327533243</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3448125624019617</v>
+        <v>0.3411443436530046</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2479844109944628</v>
+        <v>0.2498844109944628</v>
       </c>
       <c r="C96">
-        <v>-2132.380084763725</v>
+        <v>-2180.42458480598</v>
       </c>
       <c r="D96">
-        <v>1088.559915236276</v>
+        <v>1079.925415194021</v>
       </c>
       <c r="E96">
-        <v>2875.440000000001</v>
+        <v>2914.85</v>
       </c>
       <c r="F96">
-        <v>3704.54</v>
+        <v>3743.95</v>
       </c>
       <c r="G96">
         <v>483.6</v>
@@ -9165,37 +9165,37 @@
         <v>298</v>
       </c>
       <c r="M96">
-        <v>873.5305320000001</v>
+        <v>882.8234100000001</v>
       </c>
       <c r="N96">
-        <v>-575.5305320000001</v>
+        <v>-584.8234100000001</v>
       </c>
       <c r="O96">
-        <v>-115.1061064</v>
+        <v>-116.964682</v>
       </c>
       <c r="P96">
-        <v>-460.4244256000001</v>
+        <v>-467.858728</v>
       </c>
       <c r="Q96">
-        <v>-250.8244256000001</v>
+        <v>-258.258728</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.690924603438966</v>
+        <v>0.8199495241267596</v>
       </c>
       <c r="T96">
-        <v>13.26444085211509</v>
+        <v>15.91732902253811</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.06822886873060093</v>
+        <v>0.06751067011238408</v>
       </c>
       <c r="W96">
-        <v>0.2197116327533243</v>
+        <v>0.2198809839874998</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3411443436530046</v>
+        <v>0.3375533505619204</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2498844109944628</v>
+        <v>0.2517844109944628</v>
       </c>
       <c r="C97">
-        <v>-2180.42458480598</v>
+        <v>-2228.333184428143</v>
       </c>
       <c r="D97">
-        <v>1079.925415194021</v>
+        <v>1071.426815571857</v>
       </c>
       <c r="E97">
-        <v>2914.85</v>
+        <v>2954.26</v>
       </c>
       <c r="F97">
-        <v>3743.95</v>
+        <v>3783.36</v>
       </c>
       <c r="G97">
         <v>483.6</v>
@@ -9247,37 +9247,37 @@
         <v>298</v>
       </c>
       <c r="M97">
-        <v>882.8234100000001</v>
+        <v>892.1162880000001</v>
       </c>
       <c r="N97">
-        <v>-584.8234100000001</v>
+        <v>-594.1162880000001</v>
       </c>
       <c r="O97">
-        <v>-116.964682</v>
+        <v>-118.8232576</v>
       </c>
       <c r="P97">
-        <v>-467.858728</v>
+        <v>-475.2930304</v>
       </c>
       <c r="Q97">
-        <v>-258.258728</v>
+        <v>-265.6930304</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.8199495241267596</v>
+        <v>1.01348690515845</v>
       </c>
       <c r="T97">
-        <v>15.91732902253811</v>
+        <v>19.89666127817265</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.06751067011238408</v>
+        <v>0.06680743396538008</v>
       </c>
       <c r="W97">
-        <v>0.2198809839874998</v>
+        <v>0.2200468070709634</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3375533505619204</v>
+        <v>0.3340371698269003</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2517844109944627</v>
+        <v>0.2536844109944628</v>
       </c>
       <c r="C98">
-        <v>-2228.333184428142</v>
+        <v>-2276.109067030919</v>
       </c>
       <c r="D98">
-        <v>1071.426815571858</v>
+        <v>1063.060932969081</v>
       </c>
       <c r="E98">
-        <v>2954.26</v>
+        <v>2993.67</v>
       </c>
       <c r="F98">
-        <v>3783.36</v>
+        <v>3822.77</v>
       </c>
       <c r="G98">
         <v>483.6</v>
@@ -9329,37 +9329,37 @@
         <v>298</v>
       </c>
       <c r="M98">
-        <v>892.1162879999999</v>
+        <v>901.409166</v>
       </c>
       <c r="N98">
-        <v>-594.1162879999999</v>
+        <v>-603.409166</v>
       </c>
       <c r="O98">
-        <v>-118.8232576</v>
+        <v>-120.6818332</v>
       </c>
       <c r="P98">
-        <v>-475.2930304</v>
+        <v>-482.7273328</v>
       </c>
       <c r="Q98">
-        <v>-265.6930304</v>
+        <v>-273.1273328</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.013486905158447</v>
+        <v>1.33604920687793</v>
       </c>
       <c r="T98">
-        <v>19.8966612781726</v>
+        <v>26.52888170423013</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.06680743396538009</v>
+        <v>0.06611869753274729</v>
       </c>
       <c r="W98">
-        <v>0.2200468070709634</v>
+        <v>0.2202092111217782</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3340371698269005</v>
+        <v>0.3305934876637365</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2536844109944628</v>
+        <v>0.2555844109944628</v>
       </c>
       <c r="C99">
-        <v>-2276.109067030919</v>
+        <v>-2323.7553173592</v>
       </c>
       <c r="D99">
-        <v>1063.060932969081</v>
+        <v>1054.8246826408</v>
       </c>
       <c r="E99">
-        <v>2993.67</v>
+        <v>3033.08</v>
       </c>
       <c r="F99">
-        <v>3822.77</v>
+        <v>3862.18</v>
       </c>
       <c r="G99">
         <v>483.6</v>
@@ -9411,37 +9411,37 @@
         <v>298</v>
       </c>
       <c r="M99">
-        <v>901.409166</v>
+        <v>910.702044</v>
       </c>
       <c r="N99">
-        <v>-603.409166</v>
+        <v>-612.702044</v>
       </c>
       <c r="O99">
-        <v>-120.6818332</v>
+        <v>-122.5404088</v>
       </c>
       <c r="P99">
-        <v>-482.7273328</v>
+        <v>-490.1616352</v>
       </c>
       <c r="Q99">
-        <v>-273.1273328</v>
+        <v>-280.5616352</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.33604920687793</v>
+        <v>1.981173810316895</v>
       </c>
       <c r="T99">
-        <v>26.52888170423013</v>
+        <v>39.7933225563452</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.06611869753274729</v>
+        <v>0.06544401694567846</v>
       </c>
       <c r="W99">
-        <v>0.2202092111217782</v>
+        <v>0.220368300804209</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3305934876637365</v>
+        <v>0.3272200847283923</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2555844109944628</v>
+        <v>0.2574844109944628</v>
       </c>
       <c r="C100">
-        <v>-2323.7553173592</v>
+        <v>-2371.274925294451</v>
       </c>
       <c r="D100">
-        <v>1054.8246826408</v>
+        <v>1046.715074705549</v>
       </c>
       <c r="E100">
-        <v>3033.08</v>
+        <v>3072.49</v>
       </c>
       <c r="F100">
-        <v>3862.18</v>
+        <v>3901.59</v>
       </c>
       <c r="G100">
         <v>483.6</v>
@@ -9493,37 +9493,37 @@
         <v>298</v>
       </c>
       <c r="M100">
-        <v>910.702044</v>
+        <v>919.9949220000001</v>
       </c>
       <c r="N100">
-        <v>-612.702044</v>
+        <v>-621.9949220000001</v>
       </c>
       <c r="O100">
-        <v>-122.5404088</v>
+        <v>-124.3989844</v>
       </c>
       <c r="P100">
-        <v>-490.1616352</v>
+        <v>-497.5959376000001</v>
       </c>
       <c r="Q100">
-        <v>-280.5616352</v>
+        <v>-287.9959376</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.981173810316895</v>
+        <v>3.916547620633789</v>
       </c>
       <c r="T100">
-        <v>39.7933225563452</v>
+        <v>79.58664511269039</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.06544401694567846</v>
+        <v>0.06478296626945947</v>
       </c>
       <c r="W100">
-        <v>0.220368300804209</v>
+        <v>0.2205241765536615</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3272200847283923</v>
+        <v>0.3239148313472974</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2574844109944628</v>
-      </c>
-      <c r="C101">
-        <v>-2371.274925294451</v>
-      </c>
-      <c r="D101">
-        <v>1046.715074705549</v>
-      </c>
-      <c r="E101">
-        <v>3072.49</v>
-      </c>
-      <c r="F101">
-        <v>3901.59</v>
-      </c>
-      <c r="G101">
-        <v>483.6</v>
-      </c>
-      <c r="H101">
-        <v>3111.9</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>507.6</v>
-      </c>
-      <c r="K101">
-        <v>209.6</v>
-      </c>
-      <c r="L101">
-        <v>298</v>
-      </c>
-      <c r="M101">
-        <v>919.9949220000001</v>
-      </c>
-      <c r="N101">
-        <v>-621.9949220000001</v>
-      </c>
-      <c r="O101">
-        <v>-124.3989844</v>
-      </c>
-      <c r="P101">
-        <v>-497.5959376000001</v>
-      </c>
-      <c r="Q101">
-        <v>-287.9959376</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.916547620633789</v>
-      </c>
-      <c r="T101">
-        <v>79.58664511269039</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.06478296626945947</v>
-      </c>
-      <c r="W101">
-        <v>0.2205241765536615</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3239148313472974</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
